--- a/Financial Analysis/LIF.xlsx
+++ b/Financial Analysis/LIF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAE5792-0558-4472-9354-D439278BC761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFABFCBE-1040-4881-9FAB-948E1FF4955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{011E3A81-6E3D-4A18-A3DD-9F9C3A2571F0}"/>
   </bookViews>
@@ -770,14 +770,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>103.11</v>
+        <v>110.37</v>
       </c>
       <c r="E3" s="3">
-        <v>45909</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45979</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>7991.0249999999996</v>
+        <v>8553.6750000000011</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -843,7 +843,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>7867.625</v>
+        <v>8430.2750000000015</v>
       </c>
     </row>
   </sheetData>
@@ -1304,115 +1304,115 @@
         <v>48.8</v>
       </c>
       <c r="G6" s="8">
-        <f>SUM(G3:G5)</f>
+        <f t="shared" ref="G6:P6" si="5">SUM(G3:G5)</f>
         <v>68.2</v>
       </c>
       <c r="H6" s="8">
-        <f>SUM(H3:H5)</f>
+        <f t="shared" si="5"/>
         <v>70.8</v>
       </c>
       <c r="I6" s="8">
-        <f>SUM(I3:I5)</f>
+        <f t="shared" si="5"/>
         <v>78.599999999999994</v>
       </c>
       <c r="J6" s="8">
-        <f>SUM(J3:J5)</f>
+        <f t="shared" si="5"/>
         <v>86.9</v>
       </c>
       <c r="K6" s="8">
-        <f>SUM(K3:K5)</f>
+        <f t="shared" si="5"/>
         <v>78.3</v>
       </c>
       <c r="L6" s="8">
-        <f>SUM(L3:L5)</f>
+        <f t="shared" si="5"/>
         <v>84.9</v>
       </c>
       <c r="M6" s="8">
-        <f>SUM(M3:M5)</f>
+        <f t="shared" si="5"/>
         <v>92.8</v>
       </c>
       <c r="N6" s="8">
-        <f>SUM(N3:N5)</f>
+        <f t="shared" si="5"/>
         <v>115.50000000000003</v>
       </c>
       <c r="O6" s="8">
-        <f>SUM(O3:O5)</f>
+        <f t="shared" si="5"/>
         <v>103.60000000000001</v>
       </c>
       <c r="P6" s="8">
-        <f>SUM(P3:P5)</f>
+        <f t="shared" si="5"/>
         <v>115.39999999999999</v>
       </c>
       <c r="Q6" s="8">
-        <f t="shared" ref="Q6:R6" si="5">SUM(Q3:Q5)</f>
+        <f t="shared" ref="Q6:R6" si="6">SUM(Q3:Q5)</f>
         <v>127.11600000000001</v>
       </c>
       <c r="R6" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>150.65400000000002</v>
       </c>
       <c r="T6" s="8">
-        <f>SUM(T3:T5)</f>
+        <f t="shared" ref="T6:Y6" si="7">SUM(T3:T5)</f>
         <v>80.7</v>
       </c>
       <c r="U6" s="8">
-        <f>SUM(U3:U5)</f>
+        <f t="shared" si="7"/>
         <v>112.69999999999999</v>
       </c>
       <c r="V6" s="8">
-        <f>SUM(V3:V5)</f>
+        <f t="shared" si="7"/>
         <v>228.3</v>
       </c>
       <c r="W6" s="8">
-        <f>SUM(W3:W5)</f>
+        <f t="shared" si="7"/>
         <v>304.5</v>
       </c>
       <c r="X6" s="8">
-        <f>SUM(X3:X5)</f>
+        <f t="shared" si="7"/>
         <v>371.50000000000006</v>
       </c>
       <c r="Y6" s="8">
-        <f>SUM(Y3:Y5)</f>
+        <f t="shared" si="7"/>
         <v>496.77</v>
       </c>
       <c r="Z6" s="8">
-        <f t="shared" ref="Z6:AI6" si="6">SUM(Z3:Z5)</f>
+        <f t="shared" ref="Z6:AI6" si="8">SUM(Z3:Z5)</f>
         <v>665.88562000000002</v>
       </c>
       <c r="AA6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>851.38445840000009</v>
       </c>
       <c r="AB6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1040.0909275680001</v>
       </c>
       <c r="AC6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1201.4628836193601</v>
       </c>
       <c r="AD6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1332.3556395917471</v>
       </c>
       <c r="AE6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1442.4435312335822</v>
       </c>
       <c r="AF6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1542.1938537366541</v>
       </c>
       <c r="AG6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1638.9609181236551</v>
       </c>
       <c r="AH6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1742.6827924059501</v>
       </c>
       <c r="AI6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1853.9218771360156</v>
       </c>
       <c r="AL6" s="10"/>
@@ -1437,7 +1437,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" ref="J7:J9" si="7">W7-I7-H7-G7</f>
+        <f t="shared" ref="J7:J9" si="9">W7-I7-H7-G7</f>
         <v>8.2999999999999972</v>
       </c>
       <c r="K7" s="5">
@@ -1483,7 +1483,7 @@
         <v>41</v>
       </c>
       <c r="Y7" s="5">
-        <f t="shared" ref="Y7:Y9" si="8">SUM(O7:R7)</f>
+        <f t="shared" ref="Y7:Y9" si="10">SUM(O7:R7)</f>
         <v>51.513960000000004</v>
       </c>
       <c r="Z7" s="5">
@@ -1495,35 +1495,35 @@
         <v>72.406230000000008</v>
       </c>
       <c r="AB7" s="5">
-        <f t="shared" ref="AB7:AI7" si="9">AB3*0.12</f>
+        <f t="shared" ref="AB7:AI7" si="11">AB3*0.12</f>
         <v>86.887476000000007</v>
       </c>
       <c r="AC7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>99.920597399999991</v>
       </c>
       <c r="AD7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>109.91265714000001</v>
       </c>
       <c r="AE7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>118.70566971120002</v>
       </c>
       <c r="AF7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>125.82800989387202</v>
       </c>
       <c r="AG7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>132.11941038856565</v>
       </c>
       <c r="AH7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>138.72538090799395</v>
       </c>
       <c r="AI7" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>145.66164995339363</v>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
         <v>11.6</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>17.699999999999996</v>
       </c>
       <c r="K8" s="5">
@@ -1593,7 +1593,7 @@
         <v>47.2</v>
       </c>
       <c r="Y8" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>46.580930000000009</v>
       </c>
       <c r="Z8" s="5">
@@ -1601,39 +1601,39 @@
         <v>47.399757000000015</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" ref="AA8:AI8" si="10">AA4*0.85</f>
+        <f t="shared" ref="AA8:AI8" si="12">AA4*0.85</f>
         <v>48.347752140000019</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>49.314707182800014</v>
       </c>
       <c r="AC8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>50.301001326456017</v>
       </c>
       <c r="AD8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>51.307021352985139</v>
       </c>
       <c r="AE8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>52.333161780044847</v>
       </c>
       <c r="AF8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>53.379825015645743</v>
       </c>
       <c r="AG8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>54.447421515958666</v>
       </c>
       <c r="AH8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>55.536369946277837</v>
       </c>
       <c r="AI8" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>56.647097345203406</v>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
         <v>0.9</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="K9" s="5">
@@ -1703,7 +1703,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="Y9" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7.2485000000000008</v>
       </c>
       <c r="Z9" s="5">
@@ -1711,39 +1711,39 @@
         <v>12.741300000000001</v>
       </c>
       <c r="AA9" s="5">
-        <f t="shared" ref="AA9:AI9" si="11">AA5*0.1</f>
+        <f t="shared" ref="AA9:AI9" si="13">AA5*0.1</f>
         <v>19.11195</v>
       </c>
       <c r="AB9" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>25.801132500000001</v>
       </c>
       <c r="AC9" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>30.961359000000002</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>35.605562849999998</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>39.166119135000002</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>43.082731048500001</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>47.391004153350003</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>52.130104568685013</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>57.343115025553516</v>
       </c>
     </row>
@@ -1760,115 +1760,115 @@
         <v>19.600000000000001</v>
       </c>
       <c r="G10" s="5">
-        <f>SUM(G7:G9)</f>
+        <f t="shared" ref="G10:P10" si="14">SUM(G7:G9)</f>
         <v>18.2</v>
       </c>
       <c r="H10" s="5">
-        <f>SUM(H7:H9)</f>
+        <f t="shared" si="14"/>
         <v>16</v>
       </c>
       <c r="I10" s="5">
-        <f>SUM(I7:I9)</f>
+        <f t="shared" si="14"/>
         <v>20.799999999999997</v>
       </c>
       <c r="J10" s="5">
-        <f>SUM(J7:J9)</f>
+        <f t="shared" si="14"/>
         <v>26.899999999999991</v>
       </c>
       <c r="K10" s="5">
-        <f>SUM(K7:K9)</f>
+        <f t="shared" si="14"/>
         <v>18.2</v>
       </c>
       <c r="L10" s="5">
-        <f>SUM(L7:L9)</f>
+        <f t="shared" si="14"/>
         <v>21.2</v>
       </c>
       <c r="M10" s="5">
-        <f>SUM(M7:M9)</f>
+        <f t="shared" si="14"/>
         <v>22.9</v>
       </c>
       <c r="N10" s="5">
-        <f>SUM(N7:N9)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="O10" s="5">
-        <f>SUM(O7:O9)</f>
+        <f t="shared" si="14"/>
         <v>20.3</v>
       </c>
       <c r="P10" s="5">
-        <f>SUM(P7:P9)</f>
+        <f t="shared" si="14"/>
         <v>24.8</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" ref="Q10:R10" si="12">SUM(Q7:Q9)</f>
+        <f t="shared" ref="Q10:R10" si="15">SUM(Q7:Q9)</f>
         <v>25.386030000000002</v>
       </c>
       <c r="R10" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>34.857360000000014</v>
       </c>
       <c r="T10" s="5">
-        <f>SUM(T7:T9)</f>
+        <f t="shared" ref="T10:Y10" si="16">SUM(T7:T9)</f>
         <v>15.4</v>
       </c>
       <c r="U10" s="5">
-        <f>SUM(U7:U9)</f>
+        <f t="shared" si="16"/>
         <v>22.700000000000003</v>
       </c>
       <c r="V10" s="5">
-        <f>SUM(V7:V9)</f>
+        <f t="shared" si="16"/>
         <v>79.699999999999989</v>
       </c>
       <c r="W10" s="5">
-        <f>SUM(W7:W9)</f>
+        <f t="shared" si="16"/>
         <v>81.900000000000006</v>
       </c>
       <c r="X10" s="5">
-        <f>SUM(X7:X9)</f>
+        <f t="shared" si="16"/>
         <v>92.3</v>
       </c>
       <c r="Y10" s="5">
-        <f>SUM(Y7:Y9)</f>
+        <f t="shared" si="16"/>
         <v>105.34339000000003</v>
       </c>
       <c r="Z10" s="5">
-        <f t="shared" ref="Z10:AI10" si="13">SUM(Z7:Z9)</f>
+        <f t="shared" ref="Z10:AI10" si="17">SUM(Z7:Z9)</f>
         <v>122.89312300000002</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>139.86593214000004</v>
       </c>
       <c r="AB10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>162.00331568280001</v>
       </c>
       <c r="AC10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>181.18295772645604</v>
       </c>
       <c r="AD10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>196.82524134298512</v>
       </c>
       <c r="AE10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>210.20495062624488</v>
       </c>
       <c r="AF10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>222.29056595801777</v>
       </c>
       <c r="AG10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>233.95783605787432</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>246.39185542295678</v>
       </c>
       <c r="AI10" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>259.65186232415056</v>
       </c>
     </row>
@@ -1885,115 +1885,115 @@
         <v>29.199999999999996</v>
       </c>
       <c r="G11" s="8">
-        <f>G6-G10</f>
+        <f t="shared" ref="G11:P11" si="18">G6-G10</f>
         <v>50</v>
       </c>
       <c r="H11" s="8">
-        <f>H6-H10</f>
+        <f t="shared" si="18"/>
         <v>54.8</v>
       </c>
       <c r="I11" s="8">
-        <f>I6-I10</f>
+        <f t="shared" si="18"/>
         <v>57.8</v>
       </c>
       <c r="J11" s="8">
-        <f>J6-J10</f>
+        <f t="shared" si="18"/>
         <v>60.000000000000014</v>
       </c>
       <c r="K11" s="8">
-        <f>K6-K10</f>
+        <f t="shared" si="18"/>
         <v>60.099999999999994</v>
       </c>
       <c r="L11" s="8">
-        <f>L6-L10</f>
+        <f t="shared" si="18"/>
         <v>63.7</v>
       </c>
       <c r="M11" s="8">
-        <f>M6-M10</f>
+        <f t="shared" si="18"/>
         <v>69.900000000000006</v>
       </c>
       <c r="N11" s="8">
-        <f>N6-N10</f>
+        <f t="shared" si="18"/>
         <v>85.500000000000028</v>
       </c>
       <c r="O11" s="8">
-        <f>O6-O10</f>
+        <f t="shared" si="18"/>
         <v>83.300000000000011</v>
       </c>
       <c r="P11" s="8">
-        <f>P6-P10</f>
+        <f t="shared" si="18"/>
         <v>90.6</v>
       </c>
       <c r="Q11" s="8">
-        <f t="shared" ref="Q11:R11" si="14">Q6-Q10</f>
+        <f t="shared" ref="Q11:R11" si="19">Q6-Q10</f>
         <v>101.72997000000001</v>
       </c>
       <c r="R11" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>115.79664000000001</v>
       </c>
       <c r="T11" s="8">
-        <f>T6-T10</f>
+        <f t="shared" ref="T11:Y11" si="20">T6-T10</f>
         <v>65.3</v>
       </c>
       <c r="U11" s="8">
-        <f>U6-U10</f>
+        <f t="shared" si="20"/>
         <v>89.999999999999986</v>
       </c>
       <c r="V11" s="8">
-        <f>V6-V10</f>
+        <f t="shared" si="20"/>
         <v>148.60000000000002</v>
       </c>
       <c r="W11" s="8">
-        <f>W6-W10</f>
+        <f t="shared" si="20"/>
         <v>222.6</v>
       </c>
       <c r="X11" s="8">
-        <f>X6-X10</f>
+        <f t="shared" si="20"/>
         <v>279.20000000000005</v>
       </c>
       <c r="Y11" s="8">
-        <f>Y6-Y10</f>
+        <f t="shared" si="20"/>
         <v>391.42660999999998</v>
       </c>
       <c r="Z11" s="8">
-        <f t="shared" ref="Z11:AI11" si="15">Z6-Z10</f>
+        <f t="shared" ref="Z11:AI11" si="21">Z6-Z10</f>
         <v>542.99249699999996</v>
       </c>
       <c r="AA11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>711.51852626000004</v>
       </c>
       <c r="AB11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>878.08761188520009</v>
       </c>
       <c r="AC11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1020.2799258929041</v>
       </c>
       <c r="AD11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1135.5303982487621</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1232.2385806073373</v>
       </c>
       <c r="AF11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1319.9032877786362</v>
       </c>
       <c r="AG11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1405.0030820657807</v>
       </c>
       <c r="AH11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1496.2909369829933</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>1594.2700148118652</v>
       </c>
       <c r="AL11" s="10"/>
@@ -2018,7 +2018,7 @@
         <v>24.6</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" ref="J12:J14" si="16">W12-I12-H12-G12</f>
+        <f t="shared" ref="J12:J14" si="22">W12-I12-H12-G12</f>
         <v>26.000000000000004</v>
       </c>
       <c r="K12" s="5">
@@ -2064,7 +2064,7 @@
         <v>113.1</v>
       </c>
       <c r="Y12" s="5">
-        <f t="shared" ref="Y12:Y14" si="17">SUM(O12:R12)</f>
+        <f t="shared" ref="Y12:Y14" si="23">SUM(O12:R12)</f>
         <v>130.31999999999996</v>
       </c>
       <c r="Z12" s="5">
@@ -2084,27 +2084,27 @@
         <v>217.60833599999995</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" ref="AD12:AI12" si="18">AC12*1.1</f>
+        <f t="shared" ref="AD12:AI12" si="24">AC12*1.1</f>
         <v>239.36916959999996</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>263.30608655999998</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>289.63669521600002</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>318.60036473760005</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>350.46040121136008</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>385.50644133249614</v>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         <v>25.7</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>25.799999999999994</v>
       </c>
       <c r="K13" s="5">
@@ -2174,7 +2174,7 @@
         <v>113.4</v>
       </c>
       <c r="Y13" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>157.81351000000001</v>
       </c>
       <c r="Z13" s="5">
@@ -2182,39 +2182,39 @@
         <v>199.76568599999999</v>
       </c>
       <c r="AA13" s="5">
-        <f t="shared" ref="AA13:AI13" si="19">AA6*0.3</f>
+        <f t="shared" ref="AA13:AI13" si="25">AA6*0.3</f>
         <v>255.41533752000001</v>
       </c>
       <c r="AB13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>312.02727827040002</v>
       </c>
       <c r="AC13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>360.438865085808</v>
       </c>
       <c r="AD13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>399.70669187752412</v>
       </c>
       <c r="AE13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>432.73305937007467</v>
       </c>
       <c r="AF13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>462.65815612099618</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>491.68827543709654</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>522.80483772178502</v>
       </c>
       <c r="AI13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>556.17656314080466</v>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         <v>14.1</v>
       </c>
       <c r="J14" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>12.8</v>
       </c>
       <c r="K14" s="5">
@@ -2284,7 +2284,7 @@
         <v>60.7</v>
       </c>
       <c r="Y14" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>71.039999999999992</v>
       </c>
       <c r="Z14" s="5">
@@ -2300,31 +2300,31 @@
         <v>100.649472</v>
       </c>
       <c r="AC14" s="5">
-        <f t="shared" ref="AC14:AI14" si="20">AB14*1.1</f>
+        <f t="shared" ref="AC14:AI14" si="26">AB14*1.1</f>
         <v>110.71441920000001</v>
       </c>
       <c r="AD14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>121.78586112000002</v>
       </c>
       <c r="AE14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>133.96444723200003</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>147.36089195520003</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>162.09698115072004</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>178.30667926579207</v>
       </c>
       <c r="AI14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>196.13734719237129</v>
       </c>
     </row>
@@ -2341,115 +2341,115 @@
         <v>62.7</v>
       </c>
       <c r="G15" s="5">
-        <f>SUM(G12:G14)</f>
+        <f t="shared" ref="G15:P15" si="27">SUM(G12:G14)</f>
         <v>64.7</v>
       </c>
       <c r="H15" s="5">
-        <f>SUM(H12:H14)</f>
+        <f t="shared" si="27"/>
         <v>59</v>
       </c>
       <c r="I15" s="5">
-        <f>SUM(I12:I14)</f>
+        <f t="shared" si="27"/>
         <v>64.399999999999991</v>
       </c>
       <c r="J15" s="5">
-        <f>SUM(J12:J14)</f>
+        <f t="shared" si="27"/>
         <v>64.599999999999994</v>
       </c>
       <c r="K15" s="5">
-        <f>SUM(K12:K14)</f>
+        <f t="shared" si="27"/>
         <v>66.400000000000006</v>
       </c>
       <c r="L15" s="5">
-        <f>SUM(L12:L14)</f>
+        <f t="shared" si="27"/>
         <v>66</v>
       </c>
       <c r="M15" s="5">
-        <f>SUM(M12:M14)</f>
+        <f t="shared" si="27"/>
         <v>74.900000000000006</v>
       </c>
       <c r="N15" s="5">
-        <f>SUM(N12:N14)</f>
+        <f t="shared" si="27"/>
         <v>79.900000000000006</v>
       </c>
       <c r="O15" s="5">
-        <f>SUM(O12:O14)</f>
+        <f t="shared" si="27"/>
         <v>81.299999999999983</v>
       </c>
       <c r="P15" s="5">
-        <f>SUM(P12:P14)</f>
+        <f t="shared" si="27"/>
         <v>88.6</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" ref="Q15:R15" si="21">SUM(Q12:Q14)</f>
+        <f t="shared" ref="Q15:R15" si="28">SUM(Q12:Q14)</f>
         <v>92.267119999999991</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>97.006389999999996</v>
       </c>
       <c r="T15" s="5">
-        <f>SUM(T12:T14)</f>
+        <f t="shared" ref="T15:Y15" si="29">SUM(T12:T14)</f>
         <v>81.899999999999991</v>
       </c>
       <c r="U15" s="5">
-        <f>SUM(U12:U14)</f>
+        <f t="shared" si="29"/>
         <v>122.2</v>
       </c>
       <c r="V15" s="5">
-        <f>SUM(V12:V14)</f>
+        <f t="shared" si="29"/>
         <v>243</v>
       </c>
       <c r="W15" s="5">
-        <f>SUM(W12:W14)</f>
+        <f t="shared" si="29"/>
         <v>252.7</v>
       </c>
       <c r="X15" s="5">
-        <f>SUM(X12:X14)</f>
+        <f t="shared" si="29"/>
         <v>287.2</v>
       </c>
       <c r="Y15" s="5">
-        <f>SUM(Y12:Y14)</f>
+        <f t="shared" si="29"/>
         <v>359.17350999999996</v>
       </c>
       <c r="Z15" s="5">
-        <f t="shared" ref="Z15:AI15" si="22">SUM(Z12:Z14)</f>
+        <f t="shared" ref="Z15:AI15" si="30">SUM(Z12:Z14)</f>
         <v>437.84568599999994</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>526.75645751999991</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>610.50251027039997</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>688.76162028580802</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>760.86172259752414</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>830.00359316207471</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>899.65574329219623</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>972.38562132541665</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>1051.5719181989373</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>1137.8203516656722</v>
       </c>
     </row>
@@ -2466,115 +2466,115 @@
         <v>-33.500000000000007</v>
       </c>
       <c r="G16" s="8">
-        <f>G11-G15</f>
+        <f t="shared" ref="G16:P16" si="31">G11-G15</f>
         <v>-14.700000000000003</v>
       </c>
       <c r="H16" s="8">
-        <f>H11-H15</f>
+        <f t="shared" si="31"/>
         <v>-4.2000000000000028</v>
       </c>
       <c r="I16" s="8">
-        <f>I11-I15</f>
+        <f t="shared" si="31"/>
         <v>-6.5999999999999943</v>
       </c>
       <c r="J16" s="8">
-        <f>J11-J15</f>
+        <f t="shared" si="31"/>
         <v>-4.5999999999999801</v>
       </c>
       <c r="K16" s="8">
-        <f>K11-K15</f>
+        <f t="shared" si="31"/>
         <v>-6.3000000000000114</v>
       </c>
       <c r="L16" s="8">
-        <f>L11-L15</f>
+        <f t="shared" si="31"/>
         <v>-2.2999999999999972</v>
       </c>
       <c r="M16" s="8">
-        <f>M11-M15</f>
+        <f t="shared" si="31"/>
         <v>-5</v>
       </c>
       <c r="N16" s="8">
-        <f>N11-N15</f>
+        <f t="shared" si="31"/>
         <v>5.6000000000000227</v>
       </c>
       <c r="O16" s="8">
-        <f>O11-O15</f>
+        <f t="shared" si="31"/>
         <v>2.0000000000000284</v>
       </c>
       <c r="P16" s="8">
-        <f>P11-P15</f>
+        <f t="shared" si="31"/>
         <v>2</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" ref="Q16:R16" si="23">Q11-Q15</f>
+        <f t="shared" ref="Q16:R16" si="32">Q11-Q15</f>
         <v>9.4628500000000173</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>18.790250000000015</v>
       </c>
       <c r="T16" s="8">
-        <f>T11-T15</f>
+        <f t="shared" ref="T16:Y16" si="33">T11-T15</f>
         <v>-16.599999999999994</v>
       </c>
       <c r="U16" s="8">
-        <f>U11-U15</f>
+        <f t="shared" si="33"/>
         <v>-32.200000000000017</v>
       </c>
       <c r="V16" s="8">
-        <f>V11-V15</f>
+        <f t="shared" si="33"/>
         <v>-94.399999999999977</v>
       </c>
       <c r="W16" s="8">
-        <f>W11-W15</f>
+        <f t="shared" si="33"/>
         <v>-30.099999999999994</v>
       </c>
       <c r="X16" s="8">
-        <f>X11-X15</f>
+        <f t="shared" si="33"/>
         <v>-7.9999999999999432</v>
       </c>
       <c r="Y16" s="8">
-        <f>Y11-Y15</f>
+        <f t="shared" si="33"/>
         <v>32.253100000000018</v>
       </c>
       <c r="Z16" s="8">
-        <f t="shared" ref="Z16:AI16" si="24">Z11-Z15</f>
+        <f t="shared" ref="Z16:AI16" si="34">Z11-Z15</f>
         <v>105.14681100000001</v>
       </c>
       <c r="AA16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>184.76206874000013</v>
       </c>
       <c r="AB16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>267.58510161480012</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>331.51830560709607</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>374.668675651238</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>402.23498744526262</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>420.24754448644001</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>432.61746074036409</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>444.71901878405606</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>456.44966314619296</v>
       </c>
       <c r="AL16" s="10"/>
@@ -2651,39 +2651,39 @@
         <v>-7.919999999999999</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" ref="AA17:AI17" si="25">Z17*1.2</f>
+        <f t="shared" ref="AA17:AI17" si="35">Z17*1.2</f>
         <v>-9.5039999999999978</v>
       </c>
       <c r="AB17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-11.404799999999996</v>
       </c>
       <c r="AC17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-13.685759999999995</v>
       </c>
       <c r="AD17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-16.422911999999993</v>
       </c>
       <c r="AE17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-19.707494399999991</v>
       </c>
       <c r="AF17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-23.648993279999988</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-28.378791935999985</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-34.054550323199983</v>
       </c>
       <c r="AI17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>-40.865460387839981</v>
       </c>
     </row>
@@ -2700,115 +2700,115 @@
         <v>-33.100000000000009</v>
       </c>
       <c r="G18" s="8">
-        <f>G16-G17</f>
+        <f t="shared" ref="G18:P18" si="36">G16-G17</f>
         <v>-13.800000000000002</v>
       </c>
       <c r="H18" s="8">
-        <f>H16-H17</f>
+        <f t="shared" si="36"/>
         <v>-4.1000000000000032</v>
       </c>
       <c r="I18" s="8">
-        <f>I16-I17</f>
+        <f t="shared" si="36"/>
         <v>-6.7999999999999945</v>
       </c>
       <c r="J18" s="8">
-        <f>J16-J17</f>
+        <f t="shared" si="36"/>
         <v>-2.99999999999998</v>
       </c>
       <c r="K18" s="8">
-        <f>K16-K17</f>
+        <f t="shared" si="36"/>
         <v>-8.3000000000000114</v>
       </c>
       <c r="L18" s="8">
-        <f>L16-L17</f>
+        <f t="shared" si="36"/>
         <v>-5.3999999999999968</v>
       </c>
       <c r="M18" s="8">
-        <f>M16-M17</f>
+        <f t="shared" si="36"/>
         <v>2.9000000000000004</v>
       </c>
       <c r="N18" s="8">
-        <f>N16-N17</f>
+        <f t="shared" si="36"/>
         <v>6.2000000000000224</v>
       </c>
       <c r="O18" s="8">
-        <f>O16-O17</f>
+        <f t="shared" si="36"/>
         <v>4.0000000000000284</v>
       </c>
       <c r="P18" s="8">
-        <f>P16-P17</f>
+        <f t="shared" si="36"/>
         <v>6.6</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" ref="Q18:R18" si="26">Q16-Q17</f>
+        <f t="shared" ref="Q18:R18" si="37">Q16-Q17</f>
         <v>9.4628500000000173</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="37"/>
         <v>18.790250000000015</v>
       </c>
       <c r="T18" s="8">
-        <f>T16-T17</f>
+        <f t="shared" ref="T18:Y18" si="38">T16-T17</f>
         <v>-16.299999999999994</v>
       </c>
       <c r="U18" s="8">
-        <f>U16-U17</f>
+        <f t="shared" si="38"/>
         <v>-33.600000000000016</v>
       </c>
       <c r="V18" s="8">
-        <f>V16-V17</f>
+        <f t="shared" si="38"/>
         <v>-91.299999999999983</v>
       </c>
       <c r="W18" s="8">
-        <f>W16-W17</f>
+        <f t="shared" si="38"/>
         <v>-27.699999999999996</v>
       </c>
       <c r="X18" s="8">
-        <f>X16-X17</f>
+        <f t="shared" si="38"/>
         <v>-4.5999999999999428</v>
       </c>
       <c r="Y18" s="8">
-        <f>Y16-Y17</f>
+        <f t="shared" si="38"/>
         <v>38.853100000000019</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" ref="Z18:AI18" si="27">Z16-Z17</f>
+        <f t="shared" ref="Z18:AI18" si="39">Z16-Z17</f>
         <v>113.06681100000002</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>194.26606874000012</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>278.98990161480015</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>345.20406560709608</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>391.091587651238</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>421.94248184526259</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>443.89653776644002</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>460.99625267636407</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>478.77356910725604</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>497.31512353403292</v>
       </c>
       <c r="AL18" s="10"/>
@@ -2887,39 +2887,39 @@
         <v>16.960021650000002</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AI19" si="28">AA18*0.15</f>
+        <f t="shared" ref="AA19:AI19" si="40">AA18*0.15</f>
         <v>29.139910311000015</v>
       </c>
       <c r="AB19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>41.848485242220022</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>51.780609841064411</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>58.663738147685699</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>63.291372276789389</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>66.584480664965994</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>69.149437901454604</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>71.8160353660884</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>74.597268530104941</v>
       </c>
     </row>
@@ -2936,115 +2936,115 @@
         <v>-33.000000000000007</v>
       </c>
       <c r="G20" s="8">
-        <f>G18-G19</f>
+        <f t="shared" ref="G20:P20" si="41">G18-G19</f>
         <v>-13.900000000000002</v>
       </c>
       <c r="H20" s="8">
-        <f>H18-H19</f>
+        <f t="shared" si="41"/>
         <v>-4.400000000000003</v>
       </c>
       <c r="I20" s="8">
-        <f>I18-I19</f>
+        <f t="shared" si="41"/>
         <v>-6.5999999999999943</v>
       </c>
       <c r="J20" s="8">
-        <f>J18-J19</f>
+        <f t="shared" si="41"/>
         <v>-3.3999999999999799</v>
       </c>
       <c r="K20" s="8">
-        <f>K18-K19</f>
+        <f t="shared" si="41"/>
         <v>-9.7000000000000117</v>
       </c>
       <c r="L20" s="8">
-        <f>L18-L19</f>
+        <f t="shared" si="41"/>
         <v>-10.899999999999997</v>
       </c>
       <c r="M20" s="8">
-        <f>M18-M19</f>
+        <f t="shared" si="41"/>
         <v>7.6000000000000005</v>
       </c>
       <c r="N20" s="8">
-        <f>N18-N19</f>
+        <f t="shared" si="41"/>
         <v>8.5000000000000213</v>
       </c>
       <c r="O20" s="8">
-        <f>O18-O19</f>
+        <f t="shared" si="41"/>
         <v>4.2000000000000286</v>
       </c>
       <c r="P20" s="8">
-        <f>P18-P19</f>
+        <f t="shared" si="41"/>
         <v>7</v>
       </c>
       <c r="Q20" s="8">
-        <f t="shared" ref="Q20:R20" si="29">Q18-Q19</f>
+        <f t="shared" ref="Q20:R20" si="42">Q18-Q19</f>
         <v>8.5165650000000159</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>16.911225000000012</v>
       </c>
       <c r="T20" s="8">
-        <f>T18-T19</f>
+        <f t="shared" ref="T20:Z20" si="43">T18-T19</f>
         <v>-16.299999999999994</v>
       </c>
       <c r="U20" s="8">
-        <f>U18-U19</f>
+        <f t="shared" si="43"/>
         <v>-33.500000000000014</v>
       </c>
       <c r="V20" s="8">
-        <f>V18-V19</f>
+        <f t="shared" si="43"/>
         <v>-91.59999999999998</v>
       </c>
       <c r="W20" s="8">
-        <f>W18-W19</f>
+        <f t="shared" si="43"/>
         <v>-28.299999999999997</v>
       </c>
       <c r="X20" s="8">
-        <f>X18-X19</f>
+        <f t="shared" si="43"/>
         <v>-4.4999999999999432</v>
       </c>
       <c r="Y20" s="8">
-        <f>Y18-Y19</f>
+        <f t="shared" si="43"/>
         <v>36.627790000000019</v>
       </c>
       <c r="Z20" s="8">
-        <f>Z18-Z19</f>
+        <f t="shared" si="43"/>
         <v>96.106789350000014</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" ref="AA20:AI20" si="30">AA18-AA19</f>
+        <f t="shared" ref="AA20:AI20" si="44">AA18-AA19</f>
         <v>165.1261584290001</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>237.14141637258012</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>293.42345576603168</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>332.4278495035523</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>358.6511095684732</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>377.31205710147401</v>
       </c>
       <c r="AG20" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>391.84681477490949</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>406.95753374116765</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>422.71785500392798</v>
       </c>
       <c r="AJ20" s="1">
@@ -3052,435 +3052,435 @@
         <v>418.49067645388868</v>
       </c>
       <c r="AK20" s="1">
-        <f t="shared" ref="AK20:CV20" si="31">AJ20*(1+$AL$26)</f>
+        <f t="shared" ref="AK20:CV20" si="45">AJ20*(1+$AL$26)</f>
         <v>414.3057696893498</v>
       </c>
       <c r="AL20" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>410.16271199245631</v>
       </c>
       <c r="AM20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>406.06108487253175</v>
       </c>
       <c r="AN20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>402.00047402380642</v>
       </c>
       <c r="AO20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>397.98046928356837</v>
       </c>
       <c r="AP20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>394.0006645907327</v>
       </c>
       <c r="AQ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>390.06065794482538</v>
       </c>
       <c r="AR20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>386.16005136537711</v>
       </c>
       <c r="AS20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>382.29845085172332</v>
       </c>
       <c r="AT20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>378.47546634320611</v>
       </c>
       <c r="AU20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>374.69071167977404</v>
       </c>
       <c r="AV20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>370.94380456297631</v>
       </c>
       <c r="AW20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>367.23436651734653</v>
       </c>
       <c r="AX20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>363.56202285217307</v>
       </c>
       <c r="AY20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>359.92640262365131</v>
       </c>
       <c r="AZ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>356.32713859741477</v>
       </c>
       <c r="BA20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>352.76386721144064</v>
       </c>
       <c r="BB20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>349.23622853932625</v>
       </c>
       <c r="BC20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>345.74386625393299</v>
       </c>
       <c r="BD20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>342.28642759139365</v>
       </c>
       <c r="BE20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>338.86356331547972</v>
       </c>
       <c r="BF20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>335.4749276823249</v>
       </c>
       <c r="BG20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>332.12017840550163</v>
       </c>
       <c r="BH20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>328.79897662144663</v>
       </c>
       <c r="BI20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>325.51098685523215</v>
       </c>
       <c r="BJ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>322.25587698667982</v>
       </c>
       <c r="BK20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>319.03331821681303</v>
       </c>
       <c r="BL20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>315.84298503464487</v>
       </c>
       <c r="BM20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>312.6845551842984</v>
       </c>
       <c r="BN20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>309.55770963245544</v>
       </c>
       <c r="BO20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>306.46213253613087</v>
       </c>
       <c r="BP20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>303.39751121076955</v>
       </c>
       <c r="BQ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>300.36353609866183</v>
       </c>
       <c r="BR20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>297.35990073767522</v>
       </c>
       <c r="BS20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>294.38630173029844</v>
       </c>
       <c r="BT20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>291.44243871299545</v>
       </c>
       <c r="BU20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>288.52801432586551</v>
       </c>
       <c r="BV20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>285.64273418260683</v>
       </c>
       <c r="BW20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>282.78630684078075</v>
       </c>
       <c r="BX20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>279.95844377237296</v>
       </c>
       <c r="BY20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>277.15885933464921</v>
       </c>
       <c r="BZ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>274.3872707413027</v>
       </c>
       <c r="CA20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>271.6433980338897</v>
       </c>
       <c r="CB20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>268.92696405355082</v>
       </c>
       <c r="CC20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>266.23769441301533</v>
       </c>
       <c r="CD20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>263.5753174688852</v>
       </c>
       <c r="CE20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>260.93956429419637</v>
       </c>
       <c r="CF20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>258.33016865125438</v>
       </c>
       <c r="CG20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>255.74686696474183</v>
       </c>
       <c r="CH20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>253.18939829509441</v>
       </c>
       <c r="CI20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>250.65750431214346</v>
       </c>
       <c r="CJ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>248.15092926902201</v>
       </c>
       <c r="CK20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>245.6694199763318</v>
       </c>
       <c r="CL20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>243.21272577656848</v>
       </c>
       <c r="CM20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>240.78059851880278</v>
       </c>
       <c r="CN20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>238.37279253361476</v>
       </c>
       <c r="CO20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>235.9890646082786</v>
       </c>
       <c r="CP20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>233.62917396219581</v>
       </c>
       <c r="CQ20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>231.29288222257384</v>
       </c>
       <c r="CR20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>228.97995340034811</v>
       </c>
       <c r="CS20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>226.69015386634462</v>
       </c>
       <c r="CT20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>224.42325232768115</v>
       </c>
       <c r="CU20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>222.17901980440433</v>
       </c>
       <c r="CV20" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>219.9572296063603</v>
       </c>
       <c r="CW20" s="1">
-        <f t="shared" ref="CW20:EN20" si="32">CV20*(1+$AL$26)</f>
+        <f t="shared" ref="CW20:EN20" si="46">CV20*(1+$AL$26)</f>
         <v>217.75765731029671</v>
       </c>
       <c r="CX20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>215.58008073719373</v>
       </c>
       <c r="CY20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>213.42427992982178</v>
       </c>
       <c r="CZ20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>211.29003713052356</v>
       </c>
       <c r="DA20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>209.17713675921831</v>
       </c>
       <c r="DB20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>207.08536539162614</v>
       </c>
       <c r="DC20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>205.01451173770988</v>
       </c>
       <c r="DD20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>202.96436662033278</v>
       </c>
       <c r="DE20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>200.93472295412946</v>
       </c>
       <c r="DF20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>198.92537572458815</v>
       </c>
       <c r="DG20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>196.93612196734227</v>
       </c>
       <c r="DH20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>194.96676074766884</v>
       </c>
       <c r="DI20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>193.01709314019215</v>
       </c>
       <c r="DJ20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>191.08692220879021</v>
       </c>
       <c r="DK20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>189.1760529867023</v>
       </c>
       <c r="DL20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>187.28429245683529</v>
       </c>
       <c r="DM20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>185.41144953226694</v>
       </c>
       <c r="DN20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>183.55733503694427</v>
       </c>
       <c r="DO20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>181.72176168657481</v>
       </c>
       <c r="DP20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>179.90454406970906</v>
       </c>
       <c r="DQ20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>178.10549862901198</v>
       </c>
       <c r="DR20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>176.32444364272186</v>
       </c>
       <c r="DS20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>174.56119920629465</v>
       </c>
       <c r="DT20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>172.8155872142317</v>
       </c>
       <c r="DU20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>171.08743134208939</v>
       </c>
       <c r="DV20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>169.37655702866849</v>
       </c>
       <c r="DW20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>167.68279145838179</v>
       </c>
       <c r="DX20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>166.00596354379798</v>
       </c>
       <c r="DY20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>164.34590390835999</v>
       </c>
       <c r="DZ20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>162.70244486927638</v>
       </c>
       <c r="EA20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>161.07542042058361</v>
       </c>
       <c r="EB20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>159.46466621637776</v>
       </c>
       <c r="EC20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>157.870019554214</v>
       </c>
       <c r="ED20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>156.29131935867184</v>
       </c>
       <c r="EE20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>154.72840616508512</v>
       </c>
       <c r="EF20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>153.18112210343426</v>
       </c>
       <c r="EG20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>151.64931088239993</v>
       </c>
       <c r="EH20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>150.13281777357594</v>
       </c>
       <c r="EI20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>148.63148959584018</v>
       </c>
       <c r="EJ20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>147.14517469988178</v>
       </c>
       <c r="EK20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>145.67372295288297</v>
       </c>
       <c r="EL20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>144.21698572335413</v>
       </c>
       <c r="EM20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>142.77481586612058</v>
       </c>
       <c r="EN20" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>141.34706770745936</v>
       </c>
     </row>
@@ -3497,115 +3497,115 @@
         <v>77.5</v>
       </c>
       <c r="G21" s="5">
-        <f>77.5</f>
+        <f t="shared" ref="G21:P21" si="47">77.5</f>
         <v>77.5</v>
       </c>
       <c r="H21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="I21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="J21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="K21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="L21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="M21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="N21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="O21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="P21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" ref="Q21:R21" si="33">77.5</f>
+        <f t="shared" ref="Q21:R21" si="48">77.5</f>
         <v>77.5</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="48"/>
         <v>77.5</v>
       </c>
       <c r="T21" s="5">
-        <f>77.5</f>
+        <f t="shared" ref="T21:Z21" si="49">77.5</f>
         <v>77.5</v>
       </c>
       <c r="U21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="49"/>
         <v>77.5</v>
       </c>
       <c r="V21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="49"/>
         <v>77.5</v>
       </c>
       <c r="W21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="49"/>
         <v>77.5</v>
       </c>
       <c r="X21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="49"/>
         <v>77.5</v>
       </c>
       <c r="Y21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="49"/>
         <v>77.5</v>
       </c>
       <c r="Z21" s="5">
-        <f>77.5</f>
+        <f t="shared" si="49"/>
         <v>77.5</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" ref="AA21:AI21" si="34">77.5</f>
+        <f t="shared" ref="AA21:AI21" si="50">77.5</f>
         <v>77.5</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="50"/>
         <v>77.5</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="50"/>
         <v>77.5</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="50"/>
         <v>77.5</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="50"/>
         <v>77.5</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="50"/>
         <v>77.5</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="50"/>
         <v>77.5</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="50"/>
         <v>77.5</v>
       </c>
       <c r="AI21" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="50"/>
         <v>77.5</v>
       </c>
     </row>
@@ -3622,115 +3622,115 @@
         <v>-0.42580645161290331</v>
       </c>
       <c r="G22" s="7">
-        <f>G20/G21</f>
+        <f t="shared" ref="G22:P22" si="51">G20/G21</f>
         <v>-0.17935483870967744</v>
       </c>
       <c r="H22" s="7">
-        <f>H20/H21</f>
+        <f t="shared" si="51"/>
         <v>-5.6774193548387135E-2</v>
       </c>
       <c r="I22" s="7">
-        <f>I20/I21</f>
+        <f t="shared" si="51"/>
         <v>-8.5161290322580574E-2</v>
       </c>
       <c r="J22" s="7">
-        <f>J20/J21</f>
+        <f t="shared" si="51"/>
         <v>-4.3870967741935225E-2</v>
       </c>
       <c r="K22" s="7">
-        <f>K20/K21</f>
+        <f t="shared" si="51"/>
         <v>-0.1251612903225808</v>
       </c>
       <c r="L22" s="7">
-        <f>L20/L21</f>
+        <f t="shared" si="51"/>
         <v>-0.14064516129032253</v>
       </c>
       <c r="M22" s="7">
-        <f>M20/M21</f>
+        <f t="shared" si="51"/>
         <v>9.8064516129032261E-2</v>
       </c>
       <c r="N22" s="7">
-        <f>N20/N21</f>
+        <f t="shared" si="51"/>
         <v>0.10967741935483899</v>
       </c>
       <c r="O22" s="7">
-        <f>O20/O21</f>
+        <f t="shared" si="51"/>
         <v>5.419354838709714E-2</v>
       </c>
       <c r="P22" s="7">
-        <f>P20/P21</f>
+        <f t="shared" si="51"/>
         <v>9.0322580645161285E-2</v>
       </c>
       <c r="Q22" s="7">
-        <f t="shared" ref="Q22:R22" si="35">Q20/Q21</f>
+        <f t="shared" ref="Q22:R22" si="52">Q20/Q21</f>
         <v>0.10989116129032278</v>
       </c>
       <c r="R22" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="52"/>
         <v>0.21820935483870985</v>
       </c>
       <c r="T22" s="7">
-        <f>T20/T21</f>
+        <f t="shared" ref="T22:Z22" si="53">T20/T21</f>
         <v>-0.21032258064516121</v>
       </c>
       <c r="U22" s="7">
-        <f>U20/U21</f>
+        <f t="shared" si="53"/>
         <v>-0.43225806451612919</v>
       </c>
       <c r="V22" s="7">
-        <f>V20/V21</f>
+        <f t="shared" si="53"/>
         <v>-1.1819354838709675</v>
       </c>
       <c r="W22" s="7">
-        <f>W20/W21</f>
+        <f t="shared" si="53"/>
         <v>-0.3651612903225806</v>
       </c>
       <c r="X22" s="7">
-        <f>X20/X21</f>
+        <f t="shared" si="53"/>
         <v>-5.8064516129031525E-2</v>
       </c>
       <c r="Y22" s="7">
-        <f>Y20/Y21</f>
+        <f t="shared" si="53"/>
         <v>0.47261664516129054</v>
       </c>
       <c r="Z22" s="7">
-        <f>Z20/Z21</f>
+        <f t="shared" si="53"/>
         <v>1.2400876045161293</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" ref="AA22:AI22" si="36">AA20/AA21</f>
+        <f t="shared" ref="AA22:AI22" si="54">AA20/AA21</f>
         <v>2.1306601087612917</v>
       </c>
       <c r="AB22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="54"/>
         <v>3.059889243517163</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="54"/>
         <v>3.7861091066584733</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="54"/>
         <v>4.2893916064974489</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="54"/>
         <v>4.6277562524964289</v>
       </c>
       <c r="AF22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="54"/>
         <v>4.8685426722770844</v>
       </c>
       <c r="AG22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="54"/>
         <v>5.0560879325794774</v>
       </c>
       <c r="AH22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="54"/>
         <v>5.2510649514989378</v>
       </c>
       <c r="AI22" s="7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="54"/>
         <v>5.454423935534555</v>
       </c>
     </row>
@@ -3741,33 +3741,33 @@
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="G24" s="9">
-        <f t="shared" ref="G24:O27" si="37">G3/C3-1</f>
+        <f t="shared" ref="G24:O27" si="55">G3/C3-1</f>
         <v>0.5619335347432024</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.46388888888888902</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.1914893617021276</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.24667931688804545</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.26855123674911652</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.31605351170568574</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.32954545454545459</v>
       </c>
       <c r="P24" s="9">
@@ -3775,24 +3775,24 @@
         <v>0.34855403348554015</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:R27" si="38">Q3/M3-1</f>
+        <f t="shared" ref="Q24:R27" si="56">Q3/M3-1</f>
         <v>0.35000000000000009</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.32000000000000006</v>
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9">
-        <f t="shared" ref="T24:W27" si="39">U3/T3-1</f>
+        <f t="shared" ref="U24:W27" si="57">U3/T3-1</f>
         <v>0.48034188034188019</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>0.77020785219399568</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>0.44031311154598818</v>
       </c>
       <c r="X24" s="9">
@@ -3800,47 +3800,47 @@
         <v>0.25815217391304346</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" ref="Y24:AI24" si="40">Y3/X3-1</f>
+        <f t="shared" ref="Y24:AI24" si="58">Y3/X3-1</f>
         <v>0.33662347012239024</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>0.25</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="58"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -3851,103 +3851,103 @@
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="G25" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>4.1666666666666741E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.70588235294117641</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>2.5862068965517349E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>-0.24516129032258072</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.12796208530805719</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>-0.12745098039215674</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" ref="P25:P27" si="41">P4/L4-1</f>
+        <f t="shared" ref="P25:P27" si="59">P4/L4-1</f>
         <v>3.3613445378151363E-2</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
       <c r="V25" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>46.9</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>0.21503131524008356</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" ref="X25:AI37" si="42">X4/W4-1</f>
+        <f t="shared" ref="X25:AI27" si="60">X4/W4-1</f>
         <v>-1.0309278350515538E-2</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>-5.0850694444444233E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3958,106 +3958,106 @@
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="G26" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>-0.2168674698795181</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>8.3333333333333259E-2</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.12307692307692308</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.43076923076923079</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>1.1666666666666665</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.96923076923076934</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="59"/>
         <v>0.98630136986301364</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.95</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.94999999999999973</v>
       </c>
       <c r="T26" s="9"/>
       <c r="U26" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>0.13063063063063063</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>7.9681274900398336E-2</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>-5.9040590405904148E-2</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.415686274509804</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.96080332409972291</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.8</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.5</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.35000000000000009</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK26" t="s">
@@ -4074,106 +4074,106 @@
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="G27" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.33725490196078445</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.45081967213114749</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.14809384164222861</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.19915254237288149</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.18066157760814261</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.32911392405063311</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>0.32311621966794402</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="59"/>
         <v>0.35924617196701991</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.36978448275862097</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.30436363636363617</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>0.39653035935563796</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>1.0257320319432122</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="57"/>
         <v>0.33377135348226017</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.22003284072249607</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.3372005383580079</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.34043042051653694</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.27857462727607785</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.22164659843877654</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.15515177738228059</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>0.10894448572400139</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>8.26265062949465E-2</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>6.9153710591197237E-2</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>6.2746368851451129E-2</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>6.3285141906275433E-2</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="60"/>
         <v>6.383208993329692E-2</v>
       </c>
       <c r="AK27" t="s">
@@ -4188,47 +4188,47 @@
         <v>50</v>
       </c>
       <c r="C28" s="9">
-        <f t="shared" ref="C28:D30" si="43">(C3-C7)/C3</f>
+        <f t="shared" ref="C28:D30" si="61">(C3-C7)/C3</f>
         <v>0.78549848942598188</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="61"/>
         <v>0.78055555555555556</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" ref="G28:P30" si="44">(G3-G7)/G3</f>
+        <f t="shared" ref="G28:O30" si="62">(G3-G7)/G3</f>
         <v>0.84526112185686653</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.87855787476280833</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.85335689045936391</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.86120401337792651</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.84902597402597391</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.84170471841704719</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.85097493036211691</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.86531130876747153</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.87301587301587291</v>
       </c>
       <c r="P28" s="9">
@@ -4236,27 +4236,27 @@
         <v>0.85327313769751689</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" ref="Q28:R28" si="45">(Q3-Q7)/Q3</f>
+        <f t="shared" ref="Q28:R28" si="63">(Q3-Q7)/Q3</f>
         <v>0.86</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="63"/>
         <v>0.86</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28:W30" si="46">(T3-T7)/T3</f>
+        <f t="shared" ref="T28:W30" si="64">(T3-T7)/T3</f>
         <v>0.76752136752136746</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0.79445727482678985</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0.79973907371167641</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0.85960144927536231</v>
       </c>
       <c r="X28" s="9">
@@ -4264,47 +4264,47 @@
         <v>0.85241180705543562</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" ref="Y28:AI28" si="47">(Y3-Y7)/Y3</f>
+        <f t="shared" ref="Y28:AI28" si="65">(Y3-Y7)/Y3</f>
         <v>0.86126577505830648</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.87</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.87999999999999989</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.88</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.88</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.88</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.88</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.88</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.87999999999999989</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.88</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="65"/>
         <v>0.88</v>
       </c>
       <c r="AK28" t="s">
@@ -4320,120 +4320,120 @@
         <v>51</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="61"/>
         <v>0.1875</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="61"/>
         <v>-0.58823529411764719</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>5.9999999999999963E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.25161290322580648</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.16113744075829409</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.21568627450980388</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.16806722689075629</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>4.2735042735042736E-2</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.23949579831932793</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>3.3707865168539401E-2</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29:R30" si="48">(P4-P8)/P4</f>
+        <f t="shared" ref="P29:R30" si="66">(P4-P8)/P4</f>
         <v>0.17073170731707327</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="66"/>
         <v>0.1700000000000001</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="66"/>
         <v>0.16999999999999996</v>
       </c>
       <c r="T29" s="9"/>
       <c r="U29" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>-0.30000000000000004</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>5.2192066805845511E-2</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0.18556701030927841</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" ref="X29:AI30" si="49">(X4-X8)/X4</f>
+        <f t="shared" ref="X29:AI30" si="67">(X4-X8)/X4</f>
         <v>0.18055555555555552</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.14797735545353116</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.14999999999999997</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.14999999999999997</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.15000000000000005</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.15000000000000005</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.15000000000000005</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.14999999999999997</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.15000000000000008</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.15</v>
       </c>
       <c r="AK29" t="s">
@@ -4449,123 +4449,123 @@
         <v>52</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="61"/>
         <v>0.87951807228915668</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="61"/>
         <v>0.85</v>
       </c>
       <c r="G30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.87692307692307692</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.86153846153846148</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.86153846153846148</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.85</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.86153846153846148</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.87671232876712324</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.89247311827956988</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="62"/>
         <v>0.8984375</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="66"/>
         <v>0.8896551724137931</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="66"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="66"/>
         <v>0.9</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0.91891891891891886</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0.85657370517928277</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0.86715867158671578</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="64"/>
         <v>0.86274509803921573</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.88642659279778391</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.89759836123472492</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.9</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.9</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.9</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="67"/>
         <v>0.9</v>
       </c>
       <c r="AK30" t="s">
@@ -4581,47 +4581,47 @@
         <v>53</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:D31" si="50">C11/C6</f>
+        <f t="shared" ref="C31:D31" si="68">C11/C6</f>
         <v>0.68823529411764706</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="68"/>
         <v>0.59836065573770492</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" ref="G31:P31" si="51">G11/G6</f>
+        <f t="shared" ref="G31:O31" si="69">G11/G6</f>
         <v>0.73313782991202348</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="69"/>
         <v>0.77401129943502822</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="69"/>
         <v>0.73536895674300251</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="69"/>
         <v>0.6904487917146146</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="69"/>
         <v>0.76756066411238821</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="69"/>
         <v>0.75029446407538281</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="69"/>
         <v>0.75323275862068972</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="69"/>
         <v>0.74025974025974028</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="69"/>
         <v>0.80405405405405406</v>
       </c>
       <c r="P31" s="9">
@@ -4629,27 +4629,27 @@
         <v>0.78509532062391685</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" ref="Q31:R31" si="52">Q11/Q6</f>
+        <f t="shared" ref="Q31:R31" si="70">Q11/Q6</f>
         <v>0.8002924100821297</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="70"/>
         <v>0.76862638894420321</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" ref="T31:W31" si="53">T11/T6</f>
+        <f t="shared" ref="T31:W31" si="71">T11/T6</f>
         <v>0.80916976456009904</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="71"/>
         <v>0.79858030168589167</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="71"/>
         <v>0.6508979413053001</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="71"/>
         <v>0.73103448275862071</v>
       </c>
       <c r="X31" s="9">
@@ -4657,47 +4657,47 @@
         <v>0.7515477792732167</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31:AI31" si="54">Y11/Y6</f>
+        <f t="shared" ref="Y31:AI31" si="72">Y11/Y6</f>
         <v>0.78794333393723448</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.81544409533877593</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.83571942057428561</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.84424119912130624</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.84919803999217236</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.85227274498324257</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.85427162583863714</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.855860814501744</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.85725233989977123</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.85861348003397231</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="72"/>
         <v>0.85994455023894156</v>
       </c>
       <c r="AK31" t="s">
@@ -4715,33 +4715,33 @@
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="G32" s="9">
-        <f t="shared" ref="G32:O32" si="55">G12/C12-1</f>
+        <f t="shared" ref="G32:O32" si="73">G12/C12-1</f>
         <v>5.8365758754863828E-2</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="73"/>
         <v>-0.14074074074074072</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="73"/>
         <v>3.6764705882352811E-3</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="73"/>
         <v>0.1637931034482758</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="73"/>
         <v>0.17886178861788604</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="73"/>
         <v>0.14615384615384586</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="73"/>
         <v>0.11355311355311337</v>
       </c>
       <c r="P32" s="9">
@@ -4749,24 +4749,24 @@
         <v>0.19629629629629619</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" ref="Q32:R32" si="56">Q12/M12-1</f>
+        <f t="shared" ref="Q32:R32" si="74">Q12/M12-1</f>
         <v>0.14999999999999991</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="74"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="T32" s="9"/>
       <c r="U32" s="9">
-        <f t="shared" ref="T32:W32" si="57">U12/T12-1</f>
+        <f t="shared" ref="U32:W32" si="75">U12/T12-1</f>
         <v>0.28787878787878785</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="75"/>
         <v>1.0098039215686274</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="75"/>
         <v>-1.4634146341463428E-2</v>
       </c>
       <c r="X32" s="9">
@@ -4774,47 +4774,47 @@
         <v>0.11980198019801969</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" ref="Y32:AI32" si="58">Y12/X12-1</f>
+        <f t="shared" ref="Y32:AI32" si="76">Y12/X12-1</f>
         <v>0.15225464190981408</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="76"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK32" t="s">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AL32" s="13">
         <f>Main!D3</f>
-        <v>103.11</v>
+        <v>110.37</v>
       </c>
     </row>
     <row r="33" spans="2:38" x14ac:dyDescent="0.3">
@@ -4830,47 +4830,47 @@
         <v>55</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" ref="C33:D33" si="59">C13/C6</f>
+        <f t="shared" ref="C33:D33" si="77">C13/C6</f>
         <v>0.45490196078431372</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="77"/>
         <v>0.46926229508196721</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33:P33" si="60">G13/G6</f>
+        <f t="shared" ref="G33:O33" si="78">G13/G6</f>
         <v>0.35630498533724342</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>0.32909604519774016</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>0.32697201017811706</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>0.29689298043728413</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>0.31545338441890164</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>0.28739693757361601</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>0.33081896551724138</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>0.29090909090909089</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="78"/>
         <v>0.34073359073359066</v>
       </c>
       <c r="P33" s="9">
@@ -4878,27 +4878,27 @@
         <v>0.33708838821490467</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" ref="Q33:R33" si="61">Q13/Q6</f>
+        <f t="shared" ref="Q33:R33" si="79">Q13/Q6</f>
         <v>0.32</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="79"/>
         <v>0.28499999999999998</v>
       </c>
       <c r="T33" s="9">
-        <f t="shared" ref="T33:W33" si="62">T13/T6</f>
+        <f t="shared" ref="T33:W33" si="80">T13/T6</f>
         <v>0.37422552664188352</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="80"/>
         <v>0.42147293700088734</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="80"/>
         <v>0.40473061760841</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="80"/>
         <v>0.32545155993431851</v>
       </c>
       <c r="X33" s="9">
@@ -4906,47 +4906,47 @@
         <v>0.30524899057873484</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" ref="Y33:AI33" si="63">Y13/Y6</f>
+        <f t="shared" ref="Y33:AI33" si="81">Y13/Y6</f>
         <v>0.31767922781166336</v>
       </c>
       <c r="Z33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="63"/>
+        <f t="shared" si="81"/>
         <v>0.3</v>
       </c>
       <c r="AK33" s="1" t="s">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AL33" s="14">
         <f>AL31/AL32-1</f>
-        <v>-0.56879673548821663</v>
+        <v>-0.59716074473307978</v>
       </c>
     </row>
     <row r="34" spans="2:38" x14ac:dyDescent="0.3">
@@ -4964,33 +4964,33 @@
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="G34" s="9">
-        <f t="shared" ref="G34:O34" si="64">G14/C14-1</f>
+        <f t="shared" ref="G34:O34" si="82">G14/C14-1</f>
         <v>0</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="82"/>
         <v>-2.34375E-2</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="82"/>
         <v>9.090909090909105E-2</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="82"/>
         <v>0.16799999999999993</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="82"/>
         <v>7.8014184397163122E-2</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="82"/>
         <v>0.2890625</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="82"/>
         <v>8.3333333333333259E-2</v>
       </c>
       <c r="P34" s="9">
@@ -4998,24 +4998,24 @@
         <v>0.1917808219178081</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" ref="Q34:R34" si="65">Q14/M14-1</f>
+        <f t="shared" ref="Q34:R34" si="83">Q14/M14-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="T34" s="9"/>
       <c r="U34" s="9">
-        <f t="shared" ref="T34:W34" si="66">U14/T14-1</f>
+        <f t="shared" ref="U34:W34" si="84">U14/T14-1</f>
         <v>0.95867768595041314</v>
       </c>
       <c r="V34" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>1.0295358649789033</v>
       </c>
       <c r="W34" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>9.3555093555093505E-2</v>
       </c>
       <c r="X34" s="9">
@@ -5023,47 +5023,47 @@
         <v>0.1539923954372624</v>
       </c>
       <c r="Y34" s="9">
-        <f t="shared" ref="Y34:AI34" si="67">Y14/X14-1</f>
+        <f t="shared" ref="Y34:AI34" si="85">Y14/X14-1</f>
         <v>0.17034596375617772</v>
       </c>
       <c r="Z34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AA34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AB34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AD34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AF34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AG34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK34" t="s">
@@ -5078,47 +5078,47 @@
         <v>57</v>
       </c>
       <c r="C35" s="9">
-        <f t="shared" ref="C35:D35" si="68">C16/C6</f>
+        <f t="shared" ref="C35:D35" si="86">C16/C6</f>
         <v>-0.52941176470588225</v>
       </c>
       <c r="D35" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="86"/>
         <v>-0.68647540983606581</v>
       </c>
       <c r="G35" s="9">
-        <f t="shared" ref="G35:P35" si="69">G16/G6</f>
+        <f t="shared" ref="G35:O35" si="87">G16/G6</f>
         <v>-0.21554252199413493</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>-5.9322033898305128E-2</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>-8.3969465648854894E-2</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>-5.2934407364786877E-2</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>-8.045977011494268E-2</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>-2.7090694935217867E-2</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>-5.387931034482759E-2</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>4.8484848484848672E-2</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>1.9305019305019579E-2</v>
       </c>
       <c r="P35" s="9">
@@ -5126,27 +5126,27 @@
         <v>1.7331022530329292E-2</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" ref="Q35:R35" si="70">Q16/Q6</f>
+        <f t="shared" ref="Q35:R35" si="88">Q16/Q6</f>
         <v>7.4442635073476329E-2</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="88"/>
         <v>0.12472453436350851</v>
       </c>
       <c r="T35" s="9">
-        <f t="shared" ref="T35:W35" si="71">T16/T6</f>
+        <f t="shared" ref="T35:W35" si="89">T16/T6</f>
         <v>-0.20570012391573722</v>
       </c>
       <c r="U35" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="89"/>
         <v>-0.28571428571428592</v>
       </c>
       <c r="V35" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="89"/>
         <v>-0.41349102058694687</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="89"/>
         <v>-9.8850574712643663E-2</v>
       </c>
       <c r="X35" s="9">
@@ -5154,47 +5154,47 @@
         <v>-2.1534320323014649E-2</v>
       </c>
       <c r="Y35" s="9">
-        <f t="shared" ref="Y35:AI35" si="72">Y16/Y6</f>
+        <f t="shared" ref="Y35:AI35" si="90">Y16/Y6</f>
         <v>6.4925619501982848E-2</v>
       </c>
       <c r="Z35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.1579052135109931</v>
       </c>
       <c r="AA35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.21701367333768576</v>
       </c>
       <c r="AB35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.25727087365378992</v>
       </c>
       <c r="AC35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.27592887814262734</v>
       </c>
       <c r="AD35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.28120770800057698</v>
       </c>
       <c r="AE35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.27885666144675347</v>
       </c>
       <c r="AF35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.27249981801457868</v>
       </c>
       <c r="AG35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.2639583750634158</v>
       </c>
       <c r="AH35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.25519217881877199</v>
       </c>
       <c r="AI35" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="90"/>
         <v>0.24620760387774684</v>
       </c>
     </row>
@@ -5203,47 +5203,47 @@
         <v>28</v>
       </c>
       <c r="C36" s="9">
-        <f t="shared" ref="C36:D36" si="73">C19/C18</f>
+        <f t="shared" ref="C36:D36" si="91">C19/C18</f>
         <v>-3.9840637450199211E-3</v>
       </c>
       <c r="D36" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="91"/>
         <v>3.021148036253776E-3</v>
       </c>
       <c r="G36" s="9">
-        <f t="shared" ref="G36:P36" si="74">G19/G18</f>
+        <f t="shared" ref="G36:O36" si="92">G19/G18</f>
         <v>-7.2463768115942021E-3</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>-7.3170731707317013E-2</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>2.9411764705882377E-2</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>-0.13333333333333422</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>-0.16867469879518049</v>
       </c>
       <c r="L36" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>-1.018518518518519</v>
       </c>
       <c r="M36" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>-1.6206896551724137</v>
       </c>
       <c r="N36" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>-0.37096774193548243</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="92"/>
         <v>-4.9999999999999649E-2</v>
       </c>
       <c r="P36" s="9">
@@ -5251,27 +5251,27 @@
         <v>-6.0606060606060615E-2</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" ref="Q36:R36" si="75">Q19/Q18</f>
+        <f t="shared" ref="Q36:R36" si="93">Q19/Q18</f>
         <v>0.1</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="93"/>
         <v>0.1</v>
       </c>
       <c r="T36" s="9">
-        <f t="shared" ref="T36:W36" si="76">T19/T18</f>
+        <f t="shared" ref="T36:W36" si="94">T19/T18</f>
         <v>0</v>
       </c>
       <c r="U36" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="94"/>
         <v>2.9761904761904752E-3</v>
       </c>
       <c r="V36" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="94"/>
         <v>-3.2858707557502742E-3</v>
       </c>
       <c r="W36" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="94"/>
         <v>-2.1660649819494587E-2</v>
       </c>
       <c r="X36" s="9">
@@ -5279,47 +5279,47 @@
         <v>2.1739130434782879E-2</v>
       </c>
       <c r="Y36" s="9">
-        <f t="shared" ref="Y36:AI36" si="77">Y19/Y18</f>
+        <f t="shared" ref="Y36:AI36" si="95">Y19/Y18</f>
         <v>5.7274966476291517E-2</v>
       </c>
       <c r="Z36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AA36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AB36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AD36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AE36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AF36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AH36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="95"/>
         <v>0.15</v>
       </c>
     </row>
@@ -5328,47 +5328,47 @@
         <v>58</v>
       </c>
       <c r="C37" s="9">
-        <f t="shared" ref="C37:D37" si="78">C20/C6</f>
+        <f t="shared" ref="C37:D37" si="96">C20/C6</f>
         <v>-0.49411764705882344</v>
       </c>
       <c r="D37" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="96"/>
         <v>-0.67622950819672145</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" ref="G37:P37" si="79">G20/G6</f>
+        <f t="shared" ref="G37:O37" si="97">G20/G6</f>
         <v>-0.20381231671554254</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="97"/>
         <v>-6.2146892655367277E-2</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="97"/>
         <v>-8.3969465648854894E-2</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="97"/>
         <v>-3.9125431530494588E-2</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="97"/>
         <v>-0.12388250319284817</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="97"/>
         <v>-0.12838633686690218</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="97"/>
         <v>8.1896551724137942E-2</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="97"/>
         <v>7.3593073593073766E-2</v>
       </c>
       <c r="O37" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="97"/>
         <v>4.0540540540540813E-2</v>
       </c>
       <c r="P37" s="9">
@@ -5376,27 +5376,27 @@
         <v>6.0658578856152515E-2</v>
       </c>
       <c r="Q37" s="9">
-        <f t="shared" ref="Q37:R37" si="80">Q20/Q6</f>
+        <f t="shared" ref="Q37:R37" si="98">Q20/Q6</f>
         <v>6.6998371566128687E-2</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="98"/>
         <v>0.11225208092715766</v>
       </c>
       <c r="T37" s="9">
-        <f t="shared" ref="T37:W37" si="81">T20/T6</f>
+        <f t="shared" ref="T37:W37" si="99">T20/T6</f>
         <v>-0.2019826517967781</v>
       </c>
       <c r="U37" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="99"/>
         <v>-0.29724933451641544</v>
       </c>
       <c r="V37" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="99"/>
         <v>-0.40122645641699506</v>
       </c>
       <c r="W37" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="99"/>
         <v>-9.2939244663382589E-2</v>
       </c>
       <c r="X37" s="9">
@@ -5404,47 +5404,47 @@
         <v>-1.2113055181695673E-2</v>
       </c>
       <c r="Y37" s="9">
-        <f t="shared" ref="Y37:AI37" si="82">Y20/Y6</f>
+        <f t="shared" ref="Y37:AI37" si="100">Y20/Y6</f>
         <v>7.3731887996457149E-2</v>
       </c>
       <c r="Z37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.1443292758747366</v>
       </c>
       <c r="AA37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.1939501676355713</v>
       </c>
       <c r="AB37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.22800065848769366</v>
       </c>
       <c r="AC37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.24422182305133303</v>
       </c>
       <c r="AD37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.24950384088546579</v>
       </c>
       <c r="AE37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.24864135184671918</v>
       </c>
       <c r="AF37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.24465929246655138</v>
       </c>
       <c r="AG37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.23908246404283431</v>
       </c>
       <c r="AH37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.23352358531027989</v>
       </c>
       <c r="AI37" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="100"/>
         <v>0.22801276591921607</v>
       </c>
     </row>

--- a/Financial Analysis/LIF.xlsx
+++ b/Financial Analysis/LIF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFABFCBE-1040-4881-9FAB-948E1FF4955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E26C273-7015-4052-BDBE-3F67BC858434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{011E3A81-6E3D-4A18-A3DD-9F9C3A2571F0}"/>
   </bookViews>
@@ -232,7 +232,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -346,14 +346,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -370,7 +370,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10607040" y="7620"/>
+          <a:off x="11224260" y="7620"/>
           <a:ext cx="0" cy="7231380"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -770,17 +770,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>110.37</v>
+        <v>58.91</v>
       </c>
       <c r="E3" s="3">
-        <v>45937</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="3">
-        <v>45979</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -788,11 +788,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>77.5</f>
-        <v>77.5</v>
+        <f>78.4</f>
+        <v>78.400000000000006</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -801,7 +801,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>8553.6750000000011</v>
+        <v>4618.5439999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -809,11 +809,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>432.7</f>
-        <v>432.7</v>
+        <f>455.7</f>
+        <v>455.7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -821,11 +821,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>309.3</f>
-        <v>309.3</v>
+        <f>309.8</f>
+        <v>309.8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -834,7 +834,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>123.39999999999998</v>
+        <v>145.89999999999998</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -843,7 +843,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>8430.2750000000015</v>
+        <v>4472.6440000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1004,8 +1004,7 @@
         <v>88.6</v>
       </c>
       <c r="Q3" s="5">
-        <f>M3*1.35</f>
-        <v>96.93</v>
+        <v>96.3</v>
       </c>
       <c r="R3" s="5">
         <f>N3*1.32</f>
@@ -1028,47 +1027,47 @@
       </c>
       <c r="Y3" s="5">
         <f>SUM(O3:R3)</f>
-        <v>371.31400000000002</v>
+        <v>370.68400000000003</v>
       </c>
       <c r="Z3" s="5">
-        <f>Y3*1.3</f>
-        <v>482.70820000000003</v>
+        <f>Y3*1.28</f>
+        <v>474.47552000000002</v>
       </c>
       <c r="AA3" s="5">
-        <f>Z3*1.25</f>
-        <v>603.38525000000004</v>
+        <f>Z3*1.22</f>
+        <v>578.86013439999999</v>
       </c>
       <c r="AB3" s="5">
-        <f>AA3*1.2</f>
-        <v>724.06230000000005</v>
+        <f>AA3*1.15</f>
+        <v>665.68915455999991</v>
       </c>
       <c r="AC3" s="5">
-        <f>AB3*1.15</f>
-        <v>832.67164500000001</v>
+        <f>AB3*1.11</f>
+        <v>738.91496156159997</v>
       </c>
       <c r="AD3" s="5">
-        <f>AC3*1.1</f>
-        <v>915.93880950000005</v>
+        <f>AC3*1.08</f>
+        <v>798.02815848652801</v>
       </c>
       <c r="AE3" s="5">
-        <f>AD3*1.08</f>
-        <v>989.21391426000014</v>
+        <f>AD3*1.06</f>
+        <v>845.9098479957197</v>
       </c>
       <c r="AF3" s="5">
-        <f>AE3*1.06</f>
-        <v>1048.5667491156003</v>
+        <f>AE3*1.05</f>
+        <v>888.20534039550569</v>
       </c>
       <c r="AG3" s="5">
         <f>AF3*1.05</f>
-        <v>1100.9950865713804</v>
+        <v>932.61560741528103</v>
       </c>
       <c r="AH3" s="5">
         <f t="shared" ref="AH3:AI3" si="0">AG3*1.05</f>
-        <v>1156.0448408999496</v>
+        <v>979.24638778604515</v>
       </c>
       <c r="AI3" s="5">
         <f t="shared" si="0"/>
-        <v>1213.847082944947</v>
+        <v>1028.2087071753474</v>
       </c>
     </row>
     <row r="4" spans="2:38" x14ac:dyDescent="0.3">
@@ -1114,8 +1113,7 @@
         <v>12.3</v>
       </c>
       <c r="Q4" s="5">
-        <f>M4*1.03</f>
-        <v>12.051</v>
+        <v>11.3</v>
       </c>
       <c r="R4" s="5">
         <f>N4*0.9</f>
@@ -1138,47 +1136,47 @@
       </c>
       <c r="Y4" s="5">
         <f t="shared" ref="Y4:Y5" si="2">SUM(O4:R4)</f>
-        <v>54.671000000000014</v>
+        <v>53.920000000000009</v>
       </c>
       <c r="Z4" s="5">
         <f>Y4*1.02</f>
-        <v>55.764420000000015</v>
+        <v>54.998400000000011</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" ref="AA4:AI4" si="3">Z4*1.02</f>
-        <v>56.87970840000002</v>
+        <v>56.098368000000015</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="3"/>
-        <v>58.017302568000019</v>
+        <v>57.220335360000014</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" si="3"/>
-        <v>59.177648619360021</v>
+        <v>58.364742067200012</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="3"/>
-        <v>60.361201591747225</v>
+        <v>59.532036908544015</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="3"/>
-        <v>61.568425623582172</v>
+        <v>60.722677646714899</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" si="3"/>
-        <v>62.799794136053819</v>
+        <v>61.937131199649201</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="3"/>
-        <v>64.0557900187749</v>
+        <v>63.175873823642185</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="3"/>
-        <v>65.336905819150402</v>
+        <v>64.439391300115034</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="3"/>
-        <v>66.643643935533419</v>
+        <v>65.72817912611734</v>
       </c>
     </row>
     <row r="5" spans="2:38" x14ac:dyDescent="0.3">
@@ -1224,8 +1222,7 @@
         <v>14.5</v>
       </c>
       <c r="Q5" s="5">
-        <f>M5*1.95</f>
-        <v>18.135000000000002</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="R5" s="5">
         <f>N5*1.95</f>
@@ -1248,47 +1245,47 @@
       </c>
       <c r="Y5" s="5">
         <f t="shared" si="2"/>
-        <v>70.784999999999997</v>
+        <v>69.55</v>
       </c>
       <c r="Z5" s="5">
         <f>Y5*1.8</f>
-        <v>127.413</v>
+        <v>125.19</v>
       </c>
       <c r="AA5" s="5">
         <f>Z5*1.5</f>
-        <v>191.11949999999999</v>
+        <v>187.785</v>
       </c>
       <c r="AB5" s="5">
         <f>AA5*1.35</f>
-        <v>258.011325</v>
+        <v>253.50975000000003</v>
       </c>
       <c r="AC5" s="5">
         <f>AB5*1.2</f>
-        <v>309.61358999999999</v>
+        <v>304.21170000000001</v>
       </c>
       <c r="AD5" s="5">
         <f>AC5*1.15</f>
-        <v>356.05562849999995</v>
+        <v>349.84345500000001</v>
       </c>
       <c r="AE5" s="5">
         <f>AD5*1.1</f>
-        <v>391.66119134999997</v>
+        <v>384.82780050000002</v>
       </c>
       <c r="AF5" s="5">
         <f t="shared" ref="AF5:AI5" si="4">AE5*1.1</f>
-        <v>430.827310485</v>
+        <v>423.31058055000005</v>
       </c>
       <c r="AG5" s="5">
         <f t="shared" si="4"/>
-        <v>473.91004153350002</v>
+        <v>465.64163860500008</v>
       </c>
       <c r="AH5" s="5">
         <f t="shared" si="4"/>
-        <v>521.3010456868501</v>
+        <v>512.20580246550014</v>
       </c>
       <c r="AI5" s="5">
         <f t="shared" si="4"/>
-        <v>573.43115025553516</v>
+        <v>563.42638271205021</v>
       </c>
     </row>
     <row r="6" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1345,7 +1342,7 @@
       </c>
       <c r="Q6" s="8">
         <f t="shared" ref="Q6:R6" si="6">SUM(Q3:Q5)</f>
-        <v>127.11600000000001</v>
+        <v>124.5</v>
       </c>
       <c r="R6" s="8">
         <f t="shared" si="6"/>
@@ -1373,47 +1370,47 @@
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="7"/>
-        <v>496.77</v>
+        <v>494.15400000000005</v>
       </c>
       <c r="Z6" s="8">
         <f t="shared" ref="Z6:AI6" si="8">SUM(Z3:Z5)</f>
-        <v>665.88562000000002</v>
+        <v>654.66391999999996</v>
       </c>
       <c r="AA6" s="8">
         <f t="shared" si="8"/>
-        <v>851.38445840000009</v>
+        <v>822.74350240000001</v>
       </c>
       <c r="AB6" s="8">
         <f t="shared" si="8"/>
-        <v>1040.0909275680001</v>
+        <v>976.41923992</v>
       </c>
       <c r="AC6" s="8">
         <f t="shared" si="8"/>
-        <v>1201.4628836193601</v>
+        <v>1101.4914036288001</v>
       </c>
       <c r="AD6" s="8">
         <f t="shared" si="8"/>
-        <v>1332.3556395917471</v>
+        <v>1207.403650395072</v>
       </c>
       <c r="AE6" s="8">
         <f t="shared" si="8"/>
-        <v>1442.4435312335822</v>
+        <v>1291.4603261424347</v>
       </c>
       <c r="AF6" s="8">
         <f t="shared" si="8"/>
-        <v>1542.1938537366541</v>
+        <v>1373.453052145155</v>
       </c>
       <c r="AG6" s="8">
         <f t="shared" si="8"/>
-        <v>1638.9609181236551</v>
+        <v>1461.4331198439234</v>
       </c>
       <c r="AH6" s="8">
         <f t="shared" si="8"/>
-        <v>1742.6827924059501</v>
+        <v>1555.8915815516602</v>
       </c>
       <c r="AI6" s="8">
         <f t="shared" si="8"/>
-        <v>1853.9218771360156</v>
+        <v>1657.363269013515</v>
       </c>
       <c r="AL6" s="10"/>
     </row>
@@ -1460,8 +1457,7 @@
         <v>13</v>
       </c>
       <c r="Q7" s="5">
-        <f>Q3*0.14</f>
-        <v>13.570200000000002</v>
+        <v>14</v>
       </c>
       <c r="R7" s="5">
         <f>R3*0.14</f>
@@ -1484,47 +1480,47 @@
       </c>
       <c r="Y7" s="5">
         <f t="shared" ref="Y7:Y9" si="10">SUM(O7:R7)</f>
-        <v>51.513960000000004</v>
+        <v>51.943760000000005</v>
       </c>
       <c r="Z7" s="5">
         <f>Z3*0.13</f>
-        <v>62.752066000000006</v>
+        <v>61.681817600000002</v>
       </c>
       <c r="AA7" s="5">
         <f>AA3*0.12</f>
-        <v>72.406230000000008</v>
+        <v>69.463216127999999</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" ref="AB7:AI7" si="11">AB3*0.12</f>
-        <v>86.887476000000007</v>
+        <v>79.882698547199979</v>
       </c>
       <c r="AC7" s="5">
         <f t="shared" si="11"/>
-        <v>99.920597399999991</v>
+        <v>88.669795387391986</v>
       </c>
       <c r="AD7" s="5">
         <f t="shared" si="11"/>
-        <v>109.91265714000001</v>
+        <v>95.763379018383361</v>
       </c>
       <c r="AE7" s="5">
         <f t="shared" si="11"/>
-        <v>118.70566971120002</v>
+        <v>101.50918175948637</v>
       </c>
       <c r="AF7" s="5">
         <f t="shared" si="11"/>
-        <v>125.82800989387202</v>
+        <v>106.58464084746068</v>
       </c>
       <c r="AG7" s="5">
         <f t="shared" si="11"/>
-        <v>132.11941038856565</v>
+        <v>111.91387288983373</v>
       </c>
       <c r="AH7" s="5">
         <f t="shared" si="11"/>
-        <v>138.72538090799395</v>
+        <v>117.50956653432542</v>
       </c>
       <c r="AI7" s="5">
         <f t="shared" si="11"/>
-        <v>145.66164995339363</v>
+        <v>123.38504486104168</v>
       </c>
     </row>
     <row r="8" spans="2:38" x14ac:dyDescent="0.3">
@@ -1570,8 +1566,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="Q8" s="5">
-        <f>Q4*0.83</f>
-        <v>10.002329999999999</v>
+        <v>11.7</v>
       </c>
       <c r="R8" s="5">
         <f>R4*0.83</f>
@@ -1594,47 +1589,47 @@
       </c>
       <c r="Y8" s="5">
         <f t="shared" si="10"/>
-        <v>46.580930000000009</v>
+        <v>48.278600000000004</v>
       </c>
       <c r="Z8" s="5">
         <f>Z4*0.85</f>
-        <v>47.399757000000015</v>
+        <v>46.748640000000009</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" ref="AA8:AI8" si="12">AA4*0.85</f>
-        <v>48.347752140000019</v>
+        <v>47.683612800000013</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="12"/>
-        <v>49.314707182800014</v>
+        <v>48.63728505600001</v>
       </c>
       <c r="AC8" s="5">
         <f t="shared" si="12"/>
-        <v>50.301001326456017</v>
+        <v>49.610030757120008</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="12"/>
-        <v>51.307021352985139</v>
+        <v>50.602231372262409</v>
       </c>
       <c r="AE8" s="5">
         <f t="shared" si="12"/>
-        <v>52.333161780044847</v>
+        <v>51.614275999707665</v>
       </c>
       <c r="AF8" s="5">
         <f t="shared" si="12"/>
-        <v>53.379825015645743</v>
+        <v>52.64656151970182</v>
       </c>
       <c r="AG8" s="5">
         <f t="shared" si="12"/>
-        <v>54.447421515958666</v>
+        <v>53.699492750095857</v>
       </c>
       <c r="AH8" s="5">
         <f t="shared" si="12"/>
-        <v>55.536369946277837</v>
+        <v>54.773482605097776</v>
       </c>
       <c r="AI8" s="5">
         <f t="shared" si="12"/>
-        <v>56.647097345203406</v>
+        <v>55.868952257199737</v>
       </c>
     </row>
     <row r="9" spans="2:38" x14ac:dyDescent="0.3">
@@ -1680,8 +1675,7 @@
         <v>1.6</v>
       </c>
       <c r="Q9" s="5">
-        <f>Q5*0.1</f>
-        <v>1.8135000000000003</v>
+        <v>1.7</v>
       </c>
       <c r="R9" s="5">
         <f>R5*0.1</f>
@@ -1704,47 +1698,47 @@
       </c>
       <c r="Y9" s="5">
         <f t="shared" si="10"/>
-        <v>7.2485000000000008</v>
+        <v>7.1350000000000007</v>
       </c>
       <c r="Z9" s="5">
         <f>Z5*0.1</f>
-        <v>12.741300000000001</v>
+        <v>12.519</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" ref="AA9:AI9" si="13">AA5*0.1</f>
-        <v>19.11195</v>
+        <v>18.778500000000001</v>
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="13"/>
-        <v>25.801132500000001</v>
+        <v>25.350975000000005</v>
       </c>
       <c r="AC9" s="5">
         <f t="shared" si="13"/>
-        <v>30.961359000000002</v>
+        <v>30.421170000000004</v>
       </c>
       <c r="AD9" s="5">
         <f t="shared" si="13"/>
-        <v>35.605562849999998</v>
+        <v>34.984345500000003</v>
       </c>
       <c r="AE9" s="5">
         <f t="shared" si="13"/>
-        <v>39.166119135000002</v>
+        <v>38.482780050000002</v>
       </c>
       <c r="AF9" s="5">
         <f t="shared" si="13"/>
-        <v>43.082731048500001</v>
+        <v>42.331058055000007</v>
       </c>
       <c r="AG9" s="5">
         <f t="shared" si="13"/>
-        <v>47.391004153350003</v>
+        <v>46.56416386050001</v>
       </c>
       <c r="AH9" s="5">
         <f t="shared" si="13"/>
-        <v>52.130104568685013</v>
+        <v>51.220580246550014</v>
       </c>
       <c r="AI9" s="5">
         <f t="shared" si="13"/>
-        <v>57.343115025553516</v>
+        <v>56.342638271205026</v>
       </c>
     </row>
     <row r="10" spans="2:38" x14ac:dyDescent="0.3">
@@ -1801,7 +1795,7 @@
       </c>
       <c r="Q10" s="5">
         <f t="shared" ref="Q10:R10" si="15">SUM(Q7:Q9)</f>
-        <v>25.386030000000002</v>
+        <v>27.4</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="15"/>
@@ -1829,47 +1823,47 @@
       </c>
       <c r="Y10" s="5">
         <f t="shared" si="16"/>
-        <v>105.34339000000003</v>
+        <v>107.35736000000001</v>
       </c>
       <c r="Z10" s="5">
         <f t="shared" ref="Z10:AI10" si="17">SUM(Z7:Z9)</f>
-        <v>122.89312300000002</v>
+        <v>120.94945760000002</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="17"/>
-        <v>139.86593214000004</v>
+        <v>135.92532892800003</v>
       </c>
       <c r="AB10" s="5">
         <f t="shared" si="17"/>
-        <v>162.00331568280001</v>
+        <v>153.87095860319999</v>
       </c>
       <c r="AC10" s="5">
         <f t="shared" si="17"/>
-        <v>181.18295772645604</v>
+        <v>168.70099614451198</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="17"/>
-        <v>196.82524134298512</v>
+        <v>181.34995589064579</v>
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="17"/>
-        <v>210.20495062624488</v>
+        <v>191.60623780919403</v>
       </c>
       <c r="AF10" s="5">
         <f t="shared" si="17"/>
-        <v>222.29056595801777</v>
+        <v>201.5622604221625</v>
       </c>
       <c r="AG10" s="5">
         <f t="shared" si="17"/>
-        <v>233.95783605787432</v>
+        <v>212.17752950042959</v>
       </c>
       <c r="AH10" s="5">
         <f t="shared" si="17"/>
-        <v>246.39185542295678</v>
+        <v>223.5036293859732</v>
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="17"/>
-        <v>259.65186232415056</v>
+        <v>235.59663538944645</v>
       </c>
     </row>
     <row r="11" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1926,7 +1920,7 @@
       </c>
       <c r="Q11" s="8">
         <f t="shared" ref="Q11:R11" si="19">Q6-Q10</f>
-        <v>101.72997000000001</v>
+        <v>97.1</v>
       </c>
       <c r="R11" s="8">
         <f t="shared" si="19"/>
@@ -1954,47 +1948,47 @@
       </c>
       <c r="Y11" s="8">
         <f t="shared" si="20"/>
-        <v>391.42660999999998</v>
+        <v>386.79664000000002</v>
       </c>
       <c r="Z11" s="8">
         <f t="shared" ref="Z11:AI11" si="21">Z6-Z10</f>
-        <v>542.99249699999996</v>
+        <v>533.7144624</v>
       </c>
       <c r="AA11" s="8">
         <f t="shared" si="21"/>
-        <v>711.51852626000004</v>
+        <v>686.81817347200001</v>
       </c>
       <c r="AB11" s="8">
         <f t="shared" si="21"/>
-        <v>878.08761188520009</v>
+        <v>822.54828131680006</v>
       </c>
       <c r="AC11" s="8">
         <f t="shared" si="21"/>
-        <v>1020.2799258929041</v>
+        <v>932.79040748428815</v>
       </c>
       <c r="AD11" s="8">
         <f t="shared" si="21"/>
-        <v>1135.5303982487621</v>
+        <v>1026.0536945044262</v>
       </c>
       <c r="AE11" s="8">
         <f t="shared" si="21"/>
-        <v>1232.2385806073373</v>
+        <v>1099.8540883332407</v>
       </c>
       <c r="AF11" s="8">
         <f t="shared" si="21"/>
-        <v>1319.9032877786362</v>
+        <v>1171.8907917229924</v>
       </c>
       <c r="AG11" s="8">
         <f t="shared" si="21"/>
-        <v>1405.0030820657807</v>
+        <v>1249.2555903434939</v>
       </c>
       <c r="AH11" s="8">
         <f t="shared" si="21"/>
-        <v>1496.2909369829933</v>
+        <v>1332.387952165687</v>
       </c>
       <c r="AI11" s="8">
         <f t="shared" si="21"/>
-        <v>1594.2700148118652</v>
+        <v>1421.7666336240686</v>
       </c>
       <c r="AL11" s="10"/>
     </row>
@@ -2041,12 +2035,11 @@
         <v>32.299999999999997</v>
       </c>
       <c r="Q12" s="5">
-        <f>M12*1.15</f>
-        <v>33.349999999999994</v>
+        <v>32.4</v>
       </c>
       <c r="R12" s="5">
-        <f>N12*1.15</f>
-        <v>34.269999999999989</v>
+        <f>N12*1.12</f>
+        <v>33.375999999999998</v>
       </c>
       <c r="T12" s="5">
         <v>39.6</v>
@@ -2065,47 +2058,47 @@
       </c>
       <c r="Y12" s="5">
         <f t="shared" ref="Y12:Y14" si="23">SUM(O12:R12)</f>
-        <v>130.31999999999996</v>
+        <v>128.476</v>
       </c>
       <c r="Z12" s="5">
-        <f>Y12*1.2</f>
-        <v>156.38399999999996</v>
+        <f>Y12*1.12</f>
+        <v>143.89312000000001</v>
       </c>
       <c r="AA12" s="5">
-        <f>Z12*1.15</f>
-        <v>179.84159999999994</v>
+        <f>Z12*1.1</f>
+        <v>158.28243200000003</v>
       </c>
       <c r="AB12" s="5">
-        <f>AA12*1.1</f>
-        <v>197.82575999999995</v>
+        <f>AA12*1.08</f>
+        <v>170.94502656000003</v>
       </c>
       <c r="AC12" s="5">
-        <f>AB12*1.1</f>
-        <v>217.60833599999995</v>
+        <f>AB12*1.06</f>
+        <v>181.20172815360004</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" ref="AD12:AI12" si="24">AC12*1.1</f>
-        <v>239.36916959999996</v>
+        <f>AC12*1.05</f>
+        <v>190.26181456128006</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" si="24"/>
-        <v>263.30608655999998</v>
+        <f t="shared" ref="AE12:AI12" si="24">AD12*1.05</f>
+        <v>199.77490528934408</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="24"/>
-        <v>289.63669521600002</v>
+        <v>209.76365055381129</v>
       </c>
       <c r="AG12" s="5">
         <f t="shared" si="24"/>
-        <v>318.60036473760005</v>
+        <v>220.25183308150187</v>
       </c>
       <c r="AH12" s="5">
         <f t="shared" si="24"/>
-        <v>350.46040121136008</v>
+        <v>231.26442473557697</v>
       </c>
       <c r="AI12" s="5">
         <f t="shared" si="24"/>
-        <v>385.50644133249614</v>
+        <v>242.82764597235584</v>
       </c>
     </row>
     <row r="13" spans="2:38" x14ac:dyDescent="0.3">
@@ -2151,12 +2144,11 @@
         <v>38.9</v>
       </c>
       <c r="Q13" s="5">
-        <f>Q6*0.32</f>
-        <v>40.677120000000002</v>
+        <v>39</v>
       </c>
       <c r="R13" s="5">
-        <f>R6*0.285</f>
-        <v>42.936390000000003</v>
+        <f>R6*0.28</f>
+        <v>42.183120000000009</v>
       </c>
       <c r="T13" s="5">
         <v>30.2</v>
@@ -2175,47 +2167,47 @@
       </c>
       <c r="Y13" s="5">
         <f t="shared" si="23"/>
-        <v>157.81351000000001</v>
+        <v>155.38311999999999</v>
       </c>
       <c r="Z13" s="5">
-        <f>Z6*0.3</f>
-        <v>199.76568599999999</v>
+        <f>Z6*0.28</f>
+        <v>183.30589760000001</v>
       </c>
       <c r="AA13" s="5">
-        <f t="shared" ref="AA13:AI13" si="25">AA6*0.3</f>
-        <v>255.41533752000001</v>
+        <f>AA6*0.25</f>
+        <v>205.6858756</v>
       </c>
       <c r="AB13" s="5">
-        <f t="shared" si="25"/>
-        <v>312.02727827040002</v>
+        <f>AB6*0.23</f>
+        <v>224.5764251816</v>
       </c>
       <c r="AC13" s="5">
-        <f t="shared" si="25"/>
-        <v>360.438865085808</v>
+        <f>AC6*0.22</f>
+        <v>242.32810879833602</v>
       </c>
       <c r="AD13" s="5">
-        <f t="shared" si="25"/>
-        <v>399.70669187752412</v>
+        <f>AD6*0.21</f>
+        <v>253.5547665829651</v>
       </c>
       <c r="AE13" s="5">
-        <f t="shared" si="25"/>
-        <v>432.73305937007467</v>
+        <f t="shared" ref="AE13:AI13" si="25">AE6*0.21</f>
+        <v>271.20666848991129</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="25"/>
-        <v>462.65815612099618</v>
+        <v>288.42514095048256</v>
       </c>
       <c r="AG13" s="5">
         <f t="shared" si="25"/>
-        <v>491.68827543709654</v>
+        <v>306.90095516722391</v>
       </c>
       <c r="AH13" s="5">
         <f t="shared" si="25"/>
-        <v>522.80483772178502</v>
+        <v>326.73723212584866</v>
       </c>
       <c r="AI13" s="5">
         <f t="shared" si="25"/>
-        <v>556.17656314080466</v>
+        <v>348.04628649283814</v>
       </c>
     </row>
     <row r="14" spans="2:38" x14ac:dyDescent="0.3">
@@ -2261,12 +2253,11 @@
         <v>17.399999999999999</v>
       </c>
       <c r="Q14" s="5">
-        <f>M14*1.2</f>
-        <v>18.239999999999998</v>
+        <v>20</v>
       </c>
       <c r="R14" s="5">
-        <f>N14*1.2</f>
-        <v>19.8</v>
+        <f>N14*1.32</f>
+        <v>21.78</v>
       </c>
       <c r="T14" s="5">
         <v>12.1</v>
@@ -2285,47 +2276,47 @@
       </c>
       <c r="Y14" s="5">
         <f t="shared" si="23"/>
-        <v>71.039999999999992</v>
+        <v>74.78</v>
       </c>
       <c r="Z14" s="5">
         <f>Y14*1.15</f>
-        <v>81.695999999999984</v>
+        <v>85.997</v>
       </c>
       <c r="AA14" s="5">
         <f>Z14*1.12</f>
-        <v>91.49951999999999</v>
+        <v>96.316640000000007</v>
       </c>
       <c r="AB14" s="5">
         <f>AA14*1.1</f>
-        <v>100.649472</v>
+        <v>105.94830400000002</v>
       </c>
       <c r="AC14" s="5">
         <f t="shared" ref="AC14:AI14" si="26">AB14*1.1</f>
-        <v>110.71441920000001</v>
+        <v>116.54313440000003</v>
       </c>
       <c r="AD14" s="5">
         <f t="shared" si="26"/>
-        <v>121.78586112000002</v>
+        <v>128.19744784000005</v>
       </c>
       <c r="AE14" s="5">
         <f t="shared" si="26"/>
-        <v>133.96444723200003</v>
+        <v>141.01719262400007</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="26"/>
-        <v>147.36089195520003</v>
+        <v>155.1189118864001</v>
       </c>
       <c r="AG14" s="5">
         <f t="shared" si="26"/>
-        <v>162.09698115072004</v>
+        <v>170.63080307504012</v>
       </c>
       <c r="AH14" s="5">
         <f t="shared" si="26"/>
-        <v>178.30667926579207</v>
+        <v>187.69388338254416</v>
       </c>
       <c r="AI14" s="5">
         <f t="shared" si="26"/>
-        <v>196.13734719237129</v>
+        <v>206.46327172079859</v>
       </c>
     </row>
     <row r="15" spans="2:38" x14ac:dyDescent="0.3">
@@ -2382,11 +2373,11 @@
       </c>
       <c r="Q15" s="5">
         <f t="shared" ref="Q15:R15" si="28">SUM(Q12:Q14)</f>
-        <v>92.267119999999991</v>
+        <v>91.4</v>
       </c>
       <c r="R15" s="5">
         <f t="shared" si="28"/>
-        <v>97.006389999999996</v>
+        <v>97.339120000000008</v>
       </c>
       <c r="T15" s="5">
         <f t="shared" ref="T15:Y15" si="29">SUM(T12:T14)</f>
@@ -2410,47 +2401,47 @@
       </c>
       <c r="Y15" s="5">
         <f t="shared" si="29"/>
-        <v>359.17350999999996</v>
+        <v>358.63911999999993</v>
       </c>
       <c r="Z15" s="5">
         <f t="shared" ref="Z15:AI15" si="30">SUM(Z12:Z14)</f>
-        <v>437.84568599999994</v>
+        <v>413.19601760000006</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="30"/>
-        <v>526.75645751999991</v>
+        <v>460.28494760000001</v>
       </c>
       <c r="AB15" s="5">
         <f t="shared" si="30"/>
-        <v>610.50251027039997</v>
+        <v>501.46975574160001</v>
       </c>
       <c r="AC15" s="5">
         <f t="shared" si="30"/>
-        <v>688.76162028580802</v>
+        <v>540.07297135193608</v>
       </c>
       <c r="AD15" s="5">
         <f t="shared" si="30"/>
-        <v>760.86172259752414</v>
+        <v>572.01402898424521</v>
       </c>
       <c r="AE15" s="5">
         <f t="shared" si="30"/>
-        <v>830.00359316207471</v>
+        <v>611.99876640325544</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="30"/>
-        <v>899.65574329219623</v>
+        <v>653.30770339069386</v>
       </c>
       <c r="AG15" s="5">
         <f t="shared" si="30"/>
-        <v>972.38562132541665</v>
+        <v>697.7835913237659</v>
       </c>
       <c r="AH15" s="5">
         <f t="shared" si="30"/>
-        <v>1051.5719181989373</v>
+        <v>745.69554024396984</v>
       </c>
       <c r="AI15" s="5">
         <f t="shared" si="30"/>
-        <v>1137.8203516656722</v>
+        <v>797.33720418599262</v>
       </c>
     </row>
     <row r="16" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2507,11 +2498,11 @@
       </c>
       <c r="Q16" s="8">
         <f t="shared" ref="Q16:R16" si="32">Q11-Q15</f>
-        <v>9.4628500000000173</v>
+        <v>5.6999999999999886</v>
       </c>
       <c r="R16" s="8">
         <f t="shared" si="32"/>
-        <v>18.790250000000015</v>
+        <v>18.457520000000002</v>
       </c>
       <c r="T16" s="8">
         <f t="shared" ref="T16:Y16" si="33">T11-T15</f>
@@ -2535,47 +2526,47 @@
       </c>
       <c r="Y16" s="8">
         <f t="shared" si="33"/>
-        <v>32.253100000000018</v>
+        <v>28.15752000000009</v>
       </c>
       <c r="Z16" s="8">
         <f t="shared" ref="Z16:AI16" si="34">Z11-Z15</f>
-        <v>105.14681100000001</v>
+        <v>120.51844479999994</v>
       </c>
       <c r="AA16" s="8">
         <f t="shared" si="34"/>
-        <v>184.76206874000013</v>
+        <v>226.533225872</v>
       </c>
       <c r="AB16" s="8">
         <f t="shared" si="34"/>
-        <v>267.58510161480012</v>
+        <v>321.07852557520005</v>
       </c>
       <c r="AC16" s="8">
         <f t="shared" si="34"/>
-        <v>331.51830560709607</v>
+        <v>392.71743613235208</v>
       </c>
       <c r="AD16" s="8">
         <f t="shared" si="34"/>
-        <v>374.668675651238</v>
+        <v>454.03966552018096</v>
       </c>
       <c r="AE16" s="8">
         <f t="shared" si="34"/>
-        <v>402.23498744526262</v>
+        <v>487.85532192998528</v>
       </c>
       <c r="AF16" s="8">
         <f t="shared" si="34"/>
-        <v>420.24754448644001</v>
+        <v>518.58308833229853</v>
       </c>
       <c r="AG16" s="8">
         <f t="shared" si="34"/>
-        <v>432.61746074036409</v>
+        <v>551.47199901972795</v>
       </c>
       <c r="AH16" s="8">
         <f t="shared" si="34"/>
-        <v>444.71901878405606</v>
+        <v>586.69241192171717</v>
       </c>
       <c r="AI16" s="8">
         <f t="shared" si="34"/>
-        <v>456.44966314619296</v>
+        <v>624.429429438076</v>
       </c>
       <c r="AL16" s="10"/>
     </row>
@@ -2622,10 +2613,10 @@
         <v>-4.5999999999999996</v>
       </c>
       <c r="Q17" s="5">
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="R17" s="5">
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="T17" s="5">
         <v>-0.3</v>
@@ -2644,47 +2635,47 @@
       </c>
       <c r="Y17" s="5">
         <f>SUM(O17:R17)</f>
-        <v>-6.6</v>
+        <v>-15.6</v>
       </c>
       <c r="Z17" s="5">
-        <f>Y17*1.2</f>
-        <v>-7.919999999999999</v>
+        <f>-(Main!$D$6*0.05)-(Y20*0.01)</f>
+        <v>-23.201617680000002</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" ref="AA17:AI17" si="35">Z17*1.2</f>
-        <v>-9.5039999999999978</v>
+        <f>-(Main!$D$6*0.05)-(Z20*0.05)</f>
+        <v>-28.8931026554</v>
       </c>
       <c r="AB17" s="5">
-        <f t="shared" si="35"/>
-        <v>-11.404799999999996</v>
+        <f>-(Main!$D$6*0.05)-(AA20*0.05)</f>
+        <v>-33.6406189624145</v>
       </c>
       <c r="AC17" s="5">
-        <f t="shared" si="35"/>
-        <v>-13.685759999999995</v>
+        <f>-(Main!$D$6*0.05)-(AB20*0.05)</f>
+        <v>-37.860563642848618</v>
       </c>
       <c r="AD17" s="5">
-        <f t="shared" si="35"/>
-        <v>-16.422911999999993</v>
+        <f>-(Main!$D$6*0.05)-(AC20*0.05)</f>
+        <v>-41.084564990446026</v>
       </c>
       <c r="AE17" s="5">
-        <f t="shared" si="35"/>
-        <v>-19.707494399999991</v>
+        <f>-(Main!$D$6*0.05)-(AD20*0.05)</f>
+        <v>-43.827779796701648</v>
       </c>
       <c r="AF17" s="5">
-        <f t="shared" si="35"/>
-        <v>-23.648993279999988</v>
+        <f>-(Main!$D$6*0.05)-(AE20*0.05)</f>
+        <v>-45.381531823384194</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" si="35"/>
-        <v>-28.378791935999985</v>
+        <f>-(Main!$D$6*0.05)-(AF20*0.05)</f>
+        <v>-46.753496356616516</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" si="35"/>
-        <v>-34.054550323199983</v>
+        <f>-(Main!$D$6*0.05)-(AG20*0.05)</f>
+        <v>-48.209583553494639</v>
       </c>
       <c r="AI17" s="5">
-        <f t="shared" si="35"/>
-        <v>-40.865460387839981</v>
+        <f>-(Main!$D$6*0.05)-(AH20*0.05)</f>
+        <v>-49.768334807696505</v>
       </c>
     </row>
     <row r="18" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2700,116 +2691,116 @@
         <v>-33.100000000000009</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" ref="G18:P18" si="36">G16-G17</f>
+        <f t="shared" ref="G18:P18" si="35">G16-G17</f>
         <v>-13.800000000000002</v>
       </c>
       <c r="H18" s="8">
+        <f t="shared" si="35"/>
+        <v>-4.1000000000000032</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="35"/>
+        <v>-6.7999999999999945</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="35"/>
+        <v>-2.99999999999998</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="35"/>
+        <v>-8.3000000000000114</v>
+      </c>
+      <c r="L18" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.3999999999999968</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" si="35"/>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="N18" s="8">
+        <f t="shared" si="35"/>
+        <v>6.2000000000000224</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="35"/>
+        <v>4.0000000000000284</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" si="35"/>
+        <v>6.6</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" ref="Q18:R18" si="36">Q16-Q17</f>
+        <v>10.199999999999989</v>
+      </c>
+      <c r="R18" s="8">
         <f t="shared" si="36"/>
-        <v>-4.1000000000000032</v>
-      </c>
-      <c r="I18" s="8">
-        <f t="shared" si="36"/>
-        <v>-6.7999999999999945</v>
-      </c>
-      <c r="J18" s="8">
-        <f t="shared" si="36"/>
-        <v>-2.99999999999998</v>
-      </c>
-      <c r="K18" s="8">
-        <f t="shared" si="36"/>
-        <v>-8.3000000000000114</v>
-      </c>
-      <c r="L18" s="8">
-        <f t="shared" si="36"/>
-        <v>-5.3999999999999968</v>
-      </c>
-      <c r="M18" s="8">
-        <f t="shared" si="36"/>
-        <v>2.9000000000000004</v>
-      </c>
-      <c r="N18" s="8">
-        <f t="shared" si="36"/>
-        <v>6.2000000000000224</v>
-      </c>
-      <c r="O18" s="8">
-        <f t="shared" si="36"/>
-        <v>4.0000000000000284</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" si="36"/>
-        <v>6.6</v>
-      </c>
-      <c r="Q18" s="8">
-        <f t="shared" ref="Q18:R18" si="37">Q16-Q17</f>
-        <v>9.4628500000000173</v>
-      </c>
-      <c r="R18" s="8">
+        <v>22.957520000000002</v>
+      </c>
+      <c r="T18" s="8">
+        <f t="shared" ref="T18:Y18" si="37">T16-T17</f>
+        <v>-16.299999999999994</v>
+      </c>
+      <c r="U18" s="8">
         <f t="shared" si="37"/>
-        <v>18.790250000000015</v>
-      </c>
-      <c r="T18" s="8">
-        <f t="shared" ref="T18:Y18" si="38">T16-T17</f>
-        <v>-16.299999999999994</v>
-      </c>
-      <c r="U18" s="8">
+        <v>-33.600000000000016</v>
+      </c>
+      <c r="V18" s="8">
+        <f t="shared" si="37"/>
+        <v>-91.299999999999983</v>
+      </c>
+      <c r="W18" s="8">
+        <f t="shared" si="37"/>
+        <v>-27.699999999999996</v>
+      </c>
+      <c r="X18" s="8">
+        <f t="shared" si="37"/>
+        <v>-4.5999999999999428</v>
+      </c>
+      <c r="Y18" s="8">
+        <f t="shared" si="37"/>
+        <v>43.757520000000092</v>
+      </c>
+      <c r="Z18" s="8">
+        <f t="shared" ref="Z18:AI18" si="38">Z16-Z17</f>
+        <v>143.72006247999994</v>
+      </c>
+      <c r="AA18" s="8">
         <f t="shared" si="38"/>
-        <v>-33.600000000000016</v>
-      </c>
-      <c r="V18" s="8">
+        <v>255.42632852740002</v>
+      </c>
+      <c r="AB18" s="8">
         <f t="shared" si="38"/>
-        <v>-91.299999999999983</v>
-      </c>
-      <c r="W18" s="8">
+        <v>354.71914453761457</v>
+      </c>
+      <c r="AC18" s="8">
         <f t="shared" si="38"/>
-        <v>-27.699999999999996</v>
-      </c>
-      <c r="X18" s="8">
+        <v>430.57799977520068</v>
+      </c>
+      <c r="AD18" s="8">
         <f t="shared" si="38"/>
-        <v>-4.5999999999999428</v>
-      </c>
-      <c r="Y18" s="8">
+        <v>495.124230510627</v>
+      </c>
+      <c r="AE18" s="8">
         <f t="shared" si="38"/>
-        <v>38.853100000000019</v>
-      </c>
-      <c r="Z18" s="8">
-        <f t="shared" ref="Z18:AI18" si="39">Z16-Z17</f>
-        <v>113.06681100000002</v>
-      </c>
-      <c r="AA18" s="8">
-        <f t="shared" si="39"/>
-        <v>194.26606874000012</v>
-      </c>
-      <c r="AB18" s="8">
-        <f t="shared" si="39"/>
-        <v>278.98990161480015</v>
-      </c>
-      <c r="AC18" s="8">
-        <f t="shared" si="39"/>
-        <v>345.20406560709608</v>
-      </c>
-      <c r="AD18" s="8">
-        <f t="shared" si="39"/>
-        <v>391.091587651238</v>
-      </c>
-      <c r="AE18" s="8">
-        <f t="shared" si="39"/>
-        <v>421.94248184526259</v>
+        <v>531.68310172668691</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" si="39"/>
-        <v>443.89653776644002</v>
+        <f t="shared" si="38"/>
+        <v>563.96462015568272</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="39"/>
-        <v>460.99625267636407</v>
+        <f t="shared" si="38"/>
+        <v>598.2254953763445</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="39"/>
-        <v>478.77356910725604</v>
+        <f t="shared" si="38"/>
+        <v>634.90199547521183</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="39"/>
-        <v>497.31512353403292</v>
+        <f t="shared" si="38"/>
+        <v>674.19776424577253</v>
       </c>
       <c r="AL18" s="10"/>
     </row>
@@ -2856,12 +2847,11 @@
         <v>-0.4</v>
       </c>
       <c r="Q19" s="5">
-        <f>Q18*0.1</f>
-        <v>0.94628500000000182</v>
+        <v>0.4</v>
       </c>
       <c r="R19" s="5">
         <f>R18*0.1</f>
-        <v>1.8790250000000015</v>
+        <v>2.2957520000000002</v>
       </c>
       <c r="T19" s="5">
         <v>0</v>
@@ -2880,47 +2870,47 @@
       </c>
       <c r="Y19" s="5">
         <f>SUM(O19:R19)</f>
-        <v>2.225310000000003</v>
+        <v>2.0957520000000001</v>
       </c>
       <c r="Z19" s="5">
         <f>Z18*0.15</f>
-        <v>16.960021650000002</v>
+        <v>21.55800937199999</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" ref="AA19:AI19" si="40">AA18*0.15</f>
-        <v>29.139910311000015</v>
+        <f t="shared" ref="AA19:AI19" si="39">AA18*0.15</f>
+        <v>38.313949279109998</v>
       </c>
       <c r="AB19" s="5">
-        <f t="shared" si="40"/>
-        <v>41.848485242220022</v>
+        <f t="shared" si="39"/>
+        <v>53.207871680642185</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" si="40"/>
-        <v>51.780609841064411</v>
+        <f t="shared" si="39"/>
+        <v>64.586699966280094</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="40"/>
-        <v>58.663738147685699</v>
+        <f t="shared" si="39"/>
+        <v>74.268634576594053</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="40"/>
-        <v>63.291372276789389</v>
+        <f t="shared" si="39"/>
+        <v>79.752465259003031</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="40"/>
-        <v>66.584480664965994</v>
+        <f t="shared" si="39"/>
+        <v>84.594693023352406</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="40"/>
-        <v>69.149437901454604</v>
+        <f t="shared" si="39"/>
+        <v>89.733824306451666</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="40"/>
-        <v>71.8160353660884</v>
+        <f t="shared" si="39"/>
+        <v>95.235299321281772</v>
       </c>
       <c r="AI19" s="5">
-        <f t="shared" si="40"/>
-        <v>74.597268530104941</v>
+        <f t="shared" si="39"/>
+        <v>101.12966463686588</v>
       </c>
     </row>
     <row r="20" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2936,552 +2926,552 @@
         <v>-33.000000000000007</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" ref="G20:P20" si="41">G18-G19</f>
+        <f t="shared" ref="G20:P20" si="40">G18-G19</f>
         <v>-13.900000000000002</v>
       </c>
       <c r="H20" s="8">
+        <f t="shared" si="40"/>
+        <v>-4.400000000000003</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="40"/>
+        <v>-6.5999999999999943</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="40"/>
+        <v>-3.3999999999999799</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="40"/>
+        <v>-9.7000000000000117</v>
+      </c>
+      <c r="L20" s="8">
+        <f t="shared" si="40"/>
+        <v>-10.899999999999997</v>
+      </c>
+      <c r="M20" s="8">
+        <f t="shared" si="40"/>
+        <v>7.6000000000000005</v>
+      </c>
+      <c r="N20" s="8">
+        <f t="shared" si="40"/>
+        <v>8.5000000000000213</v>
+      </c>
+      <c r="O20" s="8">
+        <f t="shared" si="40"/>
+        <v>4.2000000000000286</v>
+      </c>
+      <c r="P20" s="8">
+        <f t="shared" si="40"/>
+        <v>7</v>
+      </c>
+      <c r="Q20" s="8">
+        <f t="shared" ref="Q20:R20" si="41">Q18-Q19</f>
+        <v>9.7999999999999883</v>
+      </c>
+      <c r="R20" s="8">
         <f t="shared" si="41"/>
-        <v>-4.400000000000003</v>
-      </c>
-      <c r="I20" s="8">
-        <f t="shared" si="41"/>
-        <v>-6.5999999999999943</v>
-      </c>
-      <c r="J20" s="8">
-        <f t="shared" si="41"/>
-        <v>-3.3999999999999799</v>
-      </c>
-      <c r="K20" s="8">
-        <f t="shared" si="41"/>
-        <v>-9.7000000000000117</v>
-      </c>
-      <c r="L20" s="8">
-        <f t="shared" si="41"/>
-        <v>-10.899999999999997</v>
-      </c>
-      <c r="M20" s="8">
-        <f t="shared" si="41"/>
-        <v>7.6000000000000005</v>
-      </c>
-      <c r="N20" s="8">
-        <f t="shared" si="41"/>
-        <v>8.5000000000000213</v>
-      </c>
-      <c r="O20" s="8">
-        <f t="shared" si="41"/>
-        <v>4.2000000000000286</v>
-      </c>
-      <c r="P20" s="8">
-        <f t="shared" si="41"/>
-        <v>7</v>
-      </c>
-      <c r="Q20" s="8">
-        <f t="shared" ref="Q20:R20" si="42">Q18-Q19</f>
-        <v>8.5165650000000159</v>
-      </c>
-      <c r="R20" s="8">
+        <v>20.661768000000002</v>
+      </c>
+      <c r="T20" s="8">
+        <f t="shared" ref="T20:Z20" si="42">T18-T19</f>
+        <v>-16.299999999999994</v>
+      </c>
+      <c r="U20" s="8">
         <f t="shared" si="42"/>
-        <v>16.911225000000012</v>
-      </c>
-      <c r="T20" s="8">
-        <f t="shared" ref="T20:Z20" si="43">T18-T19</f>
-        <v>-16.299999999999994</v>
-      </c>
-      <c r="U20" s="8">
+        <v>-33.500000000000014</v>
+      </c>
+      <c r="V20" s="8">
+        <f t="shared" si="42"/>
+        <v>-91.59999999999998</v>
+      </c>
+      <c r="W20" s="8">
+        <f t="shared" si="42"/>
+        <v>-28.299999999999997</v>
+      </c>
+      <c r="X20" s="8">
+        <f t="shared" si="42"/>
+        <v>-4.4999999999999432</v>
+      </c>
+      <c r="Y20" s="8">
+        <f t="shared" si="42"/>
+        <v>41.661768000000095</v>
+      </c>
+      <c r="Z20" s="8">
+        <f t="shared" si="42"/>
+        <v>122.16205310799995</v>
+      </c>
+      <c r="AA20" s="8">
+        <f t="shared" ref="AA20:AI20" si="43">AA18-AA19</f>
+        <v>217.11237924829001</v>
+      </c>
+      <c r="AB20" s="8">
         <f t="shared" si="43"/>
-        <v>-33.500000000000014</v>
-      </c>
-      <c r="V20" s="8">
+        <v>301.51127285697237</v>
+      </c>
+      <c r="AC20" s="8">
         <f t="shared" si="43"/>
-        <v>-91.59999999999998</v>
-      </c>
-      <c r="W20" s="8">
+        <v>365.99129980892059</v>
+      </c>
+      <c r="AD20" s="8">
         <f t="shared" si="43"/>
-        <v>-28.299999999999997</v>
-      </c>
-      <c r="X20" s="8">
+        <v>420.85559593403298</v>
+      </c>
+      <c r="AE20" s="8">
         <f t="shared" si="43"/>
-        <v>-4.4999999999999432</v>
-      </c>
-      <c r="Y20" s="8">
+        <v>451.93063646768388</v>
+      </c>
+      <c r="AF20" s="8">
         <f t="shared" si="43"/>
-        <v>36.627790000000019</v>
-      </c>
-      <c r="Z20" s="8">
+        <v>479.3699271323303</v>
+      </c>
+      <c r="AG20" s="8">
         <f t="shared" si="43"/>
-        <v>96.106789350000014</v>
-      </c>
-      <c r="AA20" s="8">
-        <f t="shared" ref="AA20:AI20" si="44">AA18-AA19</f>
-        <v>165.1261584290001</v>
-      </c>
-      <c r="AB20" s="8">
-        <f t="shared" si="44"/>
-        <v>237.14141637258012</v>
-      </c>
-      <c r="AC20" s="8">
-        <f t="shared" si="44"/>
-        <v>293.42345576603168</v>
-      </c>
-      <c r="AD20" s="8">
-        <f t="shared" si="44"/>
-        <v>332.4278495035523</v>
-      </c>
-      <c r="AE20" s="8">
-        <f t="shared" si="44"/>
-        <v>358.6511095684732</v>
-      </c>
-      <c r="AF20" s="8">
-        <f t="shared" si="44"/>
-        <v>377.31205710147401</v>
-      </c>
-      <c r="AG20" s="8">
-        <f t="shared" si="44"/>
-        <v>391.84681477490949</v>
+        <v>508.49167106989285</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" si="44"/>
-        <v>406.95753374116765</v>
+        <f t="shared" si="43"/>
+        <v>539.66669615393005</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="44"/>
-        <v>422.71785500392798</v>
+        <f t="shared" si="43"/>
+        <v>573.06809960890666</v>
       </c>
       <c r="AJ20" s="1">
         <f>AI20*(1+$AL$26)</f>
-        <v>418.49067645388868</v>
+        <v>567.3374186128176</v>
       </c>
       <c r="AK20" s="1">
-        <f t="shared" ref="AK20:CV20" si="45">AJ20*(1+$AL$26)</f>
-        <v>414.3057696893498</v>
+        <f t="shared" ref="AK20:CV20" si="44">AJ20*(1+$AL$26)</f>
+        <v>561.66404442668943</v>
       </c>
       <c r="AL20" s="10">
+        <f t="shared" si="44"/>
+        <v>556.04740398242257</v>
+      </c>
+      <c r="AM20" s="1">
+        <f t="shared" si="44"/>
+        <v>550.48692994259829</v>
+      </c>
+      <c r="AN20" s="1">
+        <f t="shared" si="44"/>
+        <v>544.9820606431723</v>
+      </c>
+      <c r="AO20" s="1">
+        <f t="shared" si="44"/>
+        <v>539.53224003674063</v>
+      </c>
+      <c r="AP20" s="1">
+        <f t="shared" si="44"/>
+        <v>534.13691763637325</v>
+      </c>
+      <c r="AQ20" s="1">
+        <f t="shared" si="44"/>
+        <v>528.79554846000951</v>
+      </c>
+      <c r="AR20" s="1">
+        <f t="shared" si="44"/>
+        <v>523.50759297540947</v>
+      </c>
+      <c r="AS20" s="1">
+        <f t="shared" si="44"/>
+        <v>518.27251704565538</v>
+      </c>
+      <c r="AT20" s="1">
+        <f t="shared" si="44"/>
+        <v>513.08979187519878</v>
+      </c>
+      <c r="AU20" s="1">
+        <f t="shared" si="44"/>
+        <v>507.95889395644679</v>
+      </c>
+      <c r="AV20" s="1">
+        <f t="shared" si="44"/>
+        <v>502.87930501688231</v>
+      </c>
+      <c r="AW20" s="1">
+        <f t="shared" si="44"/>
+        <v>497.8505119667135</v>
+      </c>
+      <c r="AX20" s="1">
+        <f t="shared" si="44"/>
+        <v>492.87200684704635</v>
+      </c>
+      <c r="AY20" s="1">
+        <f t="shared" si="44"/>
+        <v>487.9432867785759</v>
+      </c>
+      <c r="AZ20" s="1">
+        <f t="shared" si="44"/>
+        <v>483.06385391079016</v>
+      </c>
+      <c r="BA20" s="1">
+        <f t="shared" si="44"/>
+        <v>478.23321537168226</v>
+      </c>
+      <c r="BB20" s="1">
+        <f t="shared" si="44"/>
+        <v>473.45088321796544</v>
+      </c>
+      <c r="BC20" s="1">
+        <f t="shared" si="44"/>
+        <v>468.7163743857858</v>
+      </c>
+      <c r="BD20" s="1">
+        <f t="shared" si="44"/>
+        <v>464.02921064192793</v>
+      </c>
+      <c r="BE20" s="1">
+        <f t="shared" si="44"/>
+        <v>459.38891853550865</v>
+      </c>
+      <c r="BF20" s="1">
+        <f t="shared" si="44"/>
+        <v>454.79502935015358</v>
+      </c>
+      <c r="BG20" s="1">
+        <f t="shared" si="44"/>
+        <v>450.24707905665207</v>
+      </c>
+      <c r="BH20" s="1">
+        <f t="shared" si="44"/>
+        <v>445.74460826608555</v>
+      </c>
+      <c r="BI20" s="1">
+        <f t="shared" si="44"/>
+        <v>441.2871621834247</v>
+      </c>
+      <c r="BJ20" s="1">
+        <f t="shared" si="44"/>
+        <v>436.87429056159044</v>
+      </c>
+      <c r="BK20" s="1">
+        <f t="shared" si="44"/>
+        <v>432.50554765597451</v>
+      </c>
+      <c r="BL20" s="1">
+        <f t="shared" si="44"/>
+        <v>428.18049217941478</v>
+      </c>
+      <c r="BM20" s="1">
+        <f t="shared" si="44"/>
+        <v>423.89868725762062</v>
+      </c>
+      <c r="BN20" s="1">
+        <f t="shared" si="44"/>
+        <v>419.6597003850444</v>
+      </c>
+      <c r="BO20" s="1">
+        <f t="shared" si="44"/>
+        <v>415.46310338119395</v>
+      </c>
+      <c r="BP20" s="1">
+        <f t="shared" si="44"/>
+        <v>411.30847234738201</v>
+      </c>
+      <c r="BQ20" s="1">
+        <f t="shared" si="44"/>
+        <v>407.19538762390818</v>
+      </c>
+      <c r="BR20" s="1">
+        <f t="shared" si="44"/>
+        <v>403.12343374766908</v>
+      </c>
+      <c r="BS20" s="1">
+        <f t="shared" si="44"/>
+        <v>399.09219941019239</v>
+      </c>
+      <c r="BT20" s="1">
+        <f t="shared" si="44"/>
+        <v>395.10127741609045</v>
+      </c>
+      <c r="BU20" s="1">
+        <f t="shared" si="44"/>
+        <v>391.15026464192954</v>
+      </c>
+      <c r="BV20" s="1">
+        <f t="shared" si="44"/>
+        <v>387.23876199551023</v>
+      </c>
+      <c r="BW20" s="1">
+        <f t="shared" si="44"/>
+        <v>383.3663743755551</v>
+      </c>
+      <c r="BX20" s="1">
+        <f t="shared" si="44"/>
+        <v>379.53271063179955</v>
+      </c>
+      <c r="BY20" s="1">
+        <f t="shared" si="44"/>
+        <v>375.73738352548156</v>
+      </c>
+      <c r="BZ20" s="1">
+        <f t="shared" si="44"/>
+        <v>371.98000969022672</v>
+      </c>
+      <c r="CA20" s="1">
+        <f t="shared" si="44"/>
+        <v>368.26020959332448</v>
+      </c>
+      <c r="CB20" s="1">
+        <f t="shared" si="44"/>
+        <v>364.57760749739123</v>
+      </c>
+      <c r="CC20" s="1">
+        <f t="shared" si="44"/>
+        <v>360.9318314224173</v>
+      </c>
+      <c r="CD20" s="1">
+        <f t="shared" si="44"/>
+        <v>357.32251310819311</v>
+      </c>
+      <c r="CE20" s="1">
+        <f t="shared" si="44"/>
+        <v>353.74928797711118</v>
+      </c>
+      <c r="CF20" s="1">
+        <f t="shared" si="44"/>
+        <v>350.21179509734009</v>
+      </c>
+      <c r="CG20" s="1">
+        <f t="shared" si="44"/>
+        <v>346.70967714636669</v>
+      </c>
+      <c r="CH20" s="1">
+        <f t="shared" si="44"/>
+        <v>343.24258037490301</v>
+      </c>
+      <c r="CI20" s="1">
+        <f t="shared" si="44"/>
+        <v>339.81015457115399</v>
+      </c>
+      <c r="CJ20" s="1">
+        <f t="shared" si="44"/>
+        <v>336.41205302544245</v>
+      </c>
+      <c r="CK20" s="1">
+        <f t="shared" si="44"/>
+        <v>333.04793249518804</v>
+      </c>
+      <c r="CL20" s="1">
+        <f t="shared" si="44"/>
+        <v>329.71745317023613</v>
+      </c>
+      <c r="CM20" s="1">
+        <f t="shared" si="44"/>
+        <v>326.42027863853377</v>
+      </c>
+      <c r="CN20" s="1">
+        <f t="shared" si="44"/>
+        <v>323.15607585214843</v>
+      </c>
+      <c r="CO20" s="1">
+        <f t="shared" si="44"/>
+        <v>319.92451509362695</v>
+      </c>
+      <c r="CP20" s="1">
+        <f t="shared" si="44"/>
+        <v>316.72526994269066</v>
+      </c>
+      <c r="CQ20" s="1">
+        <f t="shared" si="44"/>
+        <v>313.55801724326375</v>
+      </c>
+      <c r="CR20" s="1">
+        <f t="shared" si="44"/>
+        <v>310.42243707083111</v>
+      </c>
+      <c r="CS20" s="1">
+        <f t="shared" si="44"/>
+        <v>307.31821270012279</v>
+      </c>
+      <c r="CT20" s="1">
+        <f t="shared" si="44"/>
+        <v>304.24503057312154</v>
+      </c>
+      <c r="CU20" s="1">
+        <f t="shared" si="44"/>
+        <v>301.20258026739032</v>
+      </c>
+      <c r="CV20" s="1">
+        <f t="shared" si="44"/>
+        <v>298.1905544647164</v>
+      </c>
+      <c r="CW20" s="1">
+        <f t="shared" ref="CW20:EN20" si="45">CV20*(1+$AL$26)</f>
+        <v>295.20864892006921</v>
+      </c>
+      <c r="CX20" s="1">
         <f t="shared" si="45"/>
-        <v>410.16271199245631</v>
-      </c>
-      <c r="AM20" s="1">
+        <v>292.25656243086854</v>
+      </c>
+      <c r="CY20" s="1">
         <f t="shared" si="45"/>
-        <v>406.06108487253175</v>
-      </c>
-      <c r="AN20" s="1">
+        <v>289.33399680655987</v>
+      </c>
+      <c r="CZ20" s="1">
         <f t="shared" si="45"/>
-        <v>402.00047402380642</v>
-      </c>
-      <c r="AO20" s="1">
+        <v>286.44065683849425</v>
+      </c>
+      <c r="DA20" s="1">
         <f t="shared" si="45"/>
-        <v>397.98046928356837</v>
-      </c>
-      <c r="AP20" s="1">
+        <v>283.57625027010931</v>
+      </c>
+      <c r="DB20" s="1">
         <f t="shared" si="45"/>
-        <v>394.0006645907327</v>
-      </c>
-      <c r="AQ20" s="1">
+        <v>280.74048776740824</v>
+      </c>
+      <c r="DC20" s="1">
         <f t="shared" si="45"/>
-        <v>390.06065794482538</v>
-      </c>
-      <c r="AR20" s="1">
+        <v>277.93308288973418</v>
+      </c>
+      <c r="DD20" s="1">
         <f t="shared" si="45"/>
-        <v>386.16005136537711</v>
-      </c>
-      <c r="AS20" s="1">
+        <v>275.15375206083684</v>
+      </c>
+      <c r="DE20" s="1">
         <f t="shared" si="45"/>
-        <v>382.29845085172332</v>
-      </c>
-      <c r="AT20" s="1">
+        <v>272.40221454022844</v>
+      </c>
+      <c r="DF20" s="1">
         <f t="shared" si="45"/>
-        <v>378.47546634320611</v>
-      </c>
-      <c r="AU20" s="1">
+        <v>269.67819239482617</v>
+      </c>
+      <c r="DG20" s="1">
         <f t="shared" si="45"/>
-        <v>374.69071167977404</v>
-      </c>
-      <c r="AV20" s="1">
+        <v>266.9814104708779</v>
+      </c>
+      <c r="DH20" s="1">
         <f t="shared" si="45"/>
-        <v>370.94380456297631</v>
-      </c>
-      <c r="AW20" s="1">
+        <v>264.31159636616911</v>
+      </c>
+      <c r="DI20" s="1">
         <f t="shared" si="45"/>
-        <v>367.23436651734653</v>
-      </c>
-      <c r="AX20" s="1">
+        <v>261.66848040250744</v>
+      </c>
+      <c r="DJ20" s="1">
         <f t="shared" si="45"/>
-        <v>363.56202285217307</v>
-      </c>
-      <c r="AY20" s="1">
+        <v>259.05179559848239</v>
+      </c>
+      <c r="DK20" s="1">
         <f t="shared" si="45"/>
-        <v>359.92640262365131</v>
-      </c>
-      <c r="AZ20" s="1">
+        <v>256.46127764249758</v>
+      </c>
+      <c r="DL20" s="1">
         <f t="shared" si="45"/>
-        <v>356.32713859741477</v>
-      </c>
-      <c r="BA20" s="1">
+        <v>253.8966648660726</v>
+      </c>
+      <c r="DM20" s="1">
         <f t="shared" si="45"/>
-        <v>352.76386721144064</v>
-      </c>
-      <c r="BB20" s="1">
+        <v>251.35769821741187</v>
+      </c>
+      <c r="DN20" s="1">
         <f t="shared" si="45"/>
-        <v>349.23622853932625</v>
-      </c>
-      <c r="BC20" s="1">
+        <v>248.84412123523774</v>
+      </c>
+      <c r="DO20" s="1">
         <f t="shared" si="45"/>
-        <v>345.74386625393299</v>
-      </c>
-      <c r="BD20" s="1">
+        <v>246.35568002288537</v>
+      </c>
+      <c r="DP20" s="1">
         <f t="shared" si="45"/>
-        <v>342.28642759139365</v>
-      </c>
-      <c r="BE20" s="1">
+        <v>243.89212322265652</v>
+      </c>
+      <c r="DQ20" s="1">
         <f t="shared" si="45"/>
-        <v>338.86356331547972</v>
-      </c>
-      <c r="BF20" s="1">
+        <v>241.45320199042996</v>
+      </c>
+      <c r="DR20" s="1">
         <f t="shared" si="45"/>
-        <v>335.4749276823249</v>
-      </c>
-      <c r="BG20" s="1">
+        <v>239.03866997052566</v>
+      </c>
+      <c r="DS20" s="1">
         <f t="shared" si="45"/>
-        <v>332.12017840550163</v>
-      </c>
-      <c r="BH20" s="1">
+        <v>236.6482832708204</v>
+      </c>
+      <c r="DT20" s="1">
         <f t="shared" si="45"/>
-        <v>328.79897662144663</v>
-      </c>
-      <c r="BI20" s="1">
+        <v>234.28180043811219</v>
+      </c>
+      <c r="DU20" s="1">
         <f t="shared" si="45"/>
-        <v>325.51098685523215</v>
-      </c>
-      <c r="BJ20" s="1">
+        <v>231.93898243373107</v>
+      </c>
+      <c r="DV20" s="1">
         <f t="shared" si="45"/>
-        <v>322.25587698667982</v>
-      </c>
-      <c r="BK20" s="1">
+        <v>229.61959260939375</v>
+      </c>
+      <c r="DW20" s="1">
         <f t="shared" si="45"/>
-        <v>319.03331821681303</v>
-      </c>
-      <c r="BL20" s="1">
+        <v>227.32339668329982</v>
+      </c>
+      <c r="DX20" s="1">
         <f t="shared" si="45"/>
-        <v>315.84298503464487</v>
-      </c>
-      <c r="BM20" s="1">
+        <v>225.05016271646682</v>
+      </c>
+      <c r="DY20" s="1">
         <f t="shared" si="45"/>
-        <v>312.6845551842984</v>
-      </c>
-      <c r="BN20" s="1">
+        <v>222.79966108930213</v>
+      </c>
+      <c r="DZ20" s="1">
         <f t="shared" si="45"/>
-        <v>309.55770963245544</v>
-      </c>
-      <c r="BO20" s="1">
+        <v>220.5716644784091</v>
+      </c>
+      <c r="EA20" s="1">
         <f t="shared" si="45"/>
-        <v>306.46213253613087</v>
-      </c>
-      <c r="BP20" s="1">
+        <v>218.365947833625</v>
+      </c>
+      <c r="EB20" s="1">
         <f t="shared" si="45"/>
-        <v>303.39751121076955</v>
-      </c>
-      <c r="BQ20" s="1">
+        <v>216.18228835528876</v>
+      </c>
+      <c r="EC20" s="1">
         <f t="shared" si="45"/>
-        <v>300.36353609866183</v>
-      </c>
-      <c r="BR20" s="1">
+        <v>214.02046547173586</v>
+      </c>
+      <c r="ED20" s="1">
         <f t="shared" si="45"/>
-        <v>297.35990073767522</v>
-      </c>
-      <c r="BS20" s="1">
+        <v>211.8802608170185</v>
+      </c>
+      <c r="EE20" s="1">
         <f t="shared" si="45"/>
-        <v>294.38630173029844</v>
-      </c>
-      <c r="BT20" s="1">
+        <v>209.7614582088483</v>
+      </c>
+      <c r="EF20" s="1">
         <f t="shared" si="45"/>
-        <v>291.44243871299545</v>
-      </c>
-      <c r="BU20" s="1">
+        <v>207.66384362675981</v>
+      </c>
+      <c r="EG20" s="1">
         <f t="shared" si="45"/>
-        <v>288.52801432586551</v>
-      </c>
-      <c r="BV20" s="1">
+        <v>205.58720519049223</v>
+      </c>
+      <c r="EH20" s="1">
         <f t="shared" si="45"/>
-        <v>285.64273418260683</v>
-      </c>
-      <c r="BW20" s="1">
+        <v>203.53133313858731</v>
+      </c>
+      <c r="EI20" s="1">
         <f t="shared" si="45"/>
-        <v>282.78630684078075</v>
-      </c>
-      <c r="BX20" s="1">
+        <v>201.49601980720144</v>
+      </c>
+      <c r="EJ20" s="1">
         <f t="shared" si="45"/>
-        <v>279.95844377237296</v>
-      </c>
-      <c r="BY20" s="1">
+        <v>199.48105960912943</v>
+      </c>
+      <c r="EK20" s="1">
         <f t="shared" si="45"/>
-        <v>277.15885933464921</v>
-      </c>
-      <c r="BZ20" s="1">
+        <v>197.48624901303813</v>
+      </c>
+      <c r="EL20" s="1">
         <f t="shared" si="45"/>
-        <v>274.3872707413027</v>
-      </c>
-      <c r="CA20" s="1">
+        <v>195.51138652290774</v>
+      </c>
+      <c r="EM20" s="1">
         <f t="shared" si="45"/>
-        <v>271.6433980338897</v>
-      </c>
-      <c r="CB20" s="1">
+        <v>193.55627265767868</v>
+      </c>
+      <c r="EN20" s="1">
         <f t="shared" si="45"/>
-        <v>268.92696405355082</v>
-      </c>
-      <c r="CC20" s="1">
-        <f t="shared" si="45"/>
-        <v>266.23769441301533</v>
-      </c>
-      <c r="CD20" s="1">
-        <f t="shared" si="45"/>
-        <v>263.5753174688852</v>
-      </c>
-      <c r="CE20" s="1">
-        <f t="shared" si="45"/>
-        <v>260.93956429419637</v>
-      </c>
-      <c r="CF20" s="1">
-        <f t="shared" si="45"/>
-        <v>258.33016865125438</v>
-      </c>
-      <c r="CG20" s="1">
-        <f t="shared" si="45"/>
-        <v>255.74686696474183</v>
-      </c>
-      <c r="CH20" s="1">
-        <f t="shared" si="45"/>
-        <v>253.18939829509441</v>
-      </c>
-      <c r="CI20" s="1">
-        <f t="shared" si="45"/>
-        <v>250.65750431214346</v>
-      </c>
-      <c r="CJ20" s="1">
-        <f t="shared" si="45"/>
-        <v>248.15092926902201</v>
-      </c>
-      <c r="CK20" s="1">
-        <f t="shared" si="45"/>
-        <v>245.6694199763318</v>
-      </c>
-      <c r="CL20" s="1">
-        <f t="shared" si="45"/>
-        <v>243.21272577656848</v>
-      </c>
-      <c r="CM20" s="1">
-        <f t="shared" si="45"/>
-        <v>240.78059851880278</v>
-      </c>
-      <c r="CN20" s="1">
-        <f t="shared" si="45"/>
-        <v>238.37279253361476</v>
-      </c>
-      <c r="CO20" s="1">
-        <f t="shared" si="45"/>
-        <v>235.9890646082786</v>
-      </c>
-      <c r="CP20" s="1">
-        <f t="shared" si="45"/>
-        <v>233.62917396219581</v>
-      </c>
-      <c r="CQ20" s="1">
-        <f t="shared" si="45"/>
-        <v>231.29288222257384</v>
-      </c>
-      <c r="CR20" s="1">
-        <f t="shared" si="45"/>
-        <v>228.97995340034811</v>
-      </c>
-      <c r="CS20" s="1">
-        <f t="shared" si="45"/>
-        <v>226.69015386634462</v>
-      </c>
-      <c r="CT20" s="1">
-        <f t="shared" si="45"/>
-        <v>224.42325232768115</v>
-      </c>
-      <c r="CU20" s="1">
-        <f t="shared" si="45"/>
-        <v>222.17901980440433</v>
-      </c>
-      <c r="CV20" s="1">
-        <f t="shared" si="45"/>
-        <v>219.9572296063603</v>
-      </c>
-      <c r="CW20" s="1">
-        <f t="shared" ref="CW20:EN20" si="46">CV20*(1+$AL$26)</f>
-        <v>217.75765731029671</v>
-      </c>
-      <c r="CX20" s="1">
-        <f t="shared" si="46"/>
-        <v>215.58008073719373</v>
-      </c>
-      <c r="CY20" s="1">
-        <f t="shared" si="46"/>
-        <v>213.42427992982178</v>
-      </c>
-      <c r="CZ20" s="1">
-        <f t="shared" si="46"/>
-        <v>211.29003713052356</v>
-      </c>
-      <c r="DA20" s="1">
-        <f t="shared" si="46"/>
-        <v>209.17713675921831</v>
-      </c>
-      <c r="DB20" s="1">
-        <f t="shared" si="46"/>
-        <v>207.08536539162614</v>
-      </c>
-      <c r="DC20" s="1">
-        <f t="shared" si="46"/>
-        <v>205.01451173770988</v>
-      </c>
-      <c r="DD20" s="1">
-        <f t="shared" si="46"/>
-        <v>202.96436662033278</v>
-      </c>
-      <c r="DE20" s="1">
-        <f t="shared" si="46"/>
-        <v>200.93472295412946</v>
-      </c>
-      <c r="DF20" s="1">
-        <f t="shared" si="46"/>
-        <v>198.92537572458815</v>
-      </c>
-      <c r="DG20" s="1">
-        <f t="shared" si="46"/>
-        <v>196.93612196734227</v>
-      </c>
-      <c r="DH20" s="1">
-        <f t="shared" si="46"/>
-        <v>194.96676074766884</v>
-      </c>
-      <c r="DI20" s="1">
-        <f t="shared" si="46"/>
-        <v>193.01709314019215</v>
-      </c>
-      <c r="DJ20" s="1">
-        <f t="shared" si="46"/>
-        <v>191.08692220879021</v>
-      </c>
-      <c r="DK20" s="1">
-        <f t="shared" si="46"/>
-        <v>189.1760529867023</v>
-      </c>
-      <c r="DL20" s="1">
-        <f t="shared" si="46"/>
-        <v>187.28429245683529</v>
-      </c>
-      <c r="DM20" s="1">
-        <f t="shared" si="46"/>
-        <v>185.41144953226694</v>
-      </c>
-      <c r="DN20" s="1">
-        <f t="shared" si="46"/>
-        <v>183.55733503694427</v>
-      </c>
-      <c r="DO20" s="1">
-        <f t="shared" si="46"/>
-        <v>181.72176168657481</v>
-      </c>
-      <c r="DP20" s="1">
-        <f t="shared" si="46"/>
-        <v>179.90454406970906</v>
-      </c>
-      <c r="DQ20" s="1">
-        <f t="shared" si="46"/>
-        <v>178.10549862901198</v>
-      </c>
-      <c r="DR20" s="1">
-        <f t="shared" si="46"/>
-        <v>176.32444364272186</v>
-      </c>
-      <c r="DS20" s="1">
-        <f t="shared" si="46"/>
-        <v>174.56119920629465</v>
-      </c>
-      <c r="DT20" s="1">
-        <f t="shared" si="46"/>
-        <v>172.8155872142317</v>
-      </c>
-      <c r="DU20" s="1">
-        <f t="shared" si="46"/>
-        <v>171.08743134208939</v>
-      </c>
-      <c r="DV20" s="1">
-        <f t="shared" si="46"/>
-        <v>169.37655702866849</v>
-      </c>
-      <c r="DW20" s="1">
-        <f t="shared" si="46"/>
-        <v>167.68279145838179</v>
-      </c>
-      <c r="DX20" s="1">
-        <f t="shared" si="46"/>
-        <v>166.00596354379798</v>
-      </c>
-      <c r="DY20" s="1">
-        <f t="shared" si="46"/>
-        <v>164.34590390835999</v>
-      </c>
-      <c r="DZ20" s="1">
-        <f t="shared" si="46"/>
-        <v>162.70244486927638</v>
-      </c>
-      <c r="EA20" s="1">
-        <f t="shared" si="46"/>
-        <v>161.07542042058361</v>
-      </c>
-      <c r="EB20" s="1">
-        <f t="shared" si="46"/>
-        <v>159.46466621637776</v>
-      </c>
-      <c r="EC20" s="1">
-        <f t="shared" si="46"/>
-        <v>157.870019554214</v>
-      </c>
-      <c r="ED20" s="1">
-        <f t="shared" si="46"/>
-        <v>156.29131935867184</v>
-      </c>
-      <c r="EE20" s="1">
-        <f t="shared" si="46"/>
-        <v>154.72840616508512</v>
-      </c>
-      <c r="EF20" s="1">
-        <f t="shared" si="46"/>
-        <v>153.18112210343426</v>
-      </c>
-      <c r="EG20" s="1">
-        <f t="shared" si="46"/>
-        <v>151.64931088239993</v>
-      </c>
-      <c r="EH20" s="1">
-        <f t="shared" si="46"/>
-        <v>150.13281777357594</v>
-      </c>
-      <c r="EI20" s="1">
-        <f t="shared" si="46"/>
-        <v>148.63148959584018</v>
-      </c>
-      <c r="EJ20" s="1">
-        <f t="shared" si="46"/>
-        <v>147.14517469988178</v>
-      </c>
-      <c r="EK20" s="1">
-        <f t="shared" si="46"/>
-        <v>145.67372295288297</v>
-      </c>
-      <c r="EL20" s="1">
-        <f t="shared" si="46"/>
-        <v>144.21698572335413</v>
-      </c>
-      <c r="EM20" s="1">
-        <f t="shared" si="46"/>
-        <v>142.77481586612058</v>
-      </c>
-      <c r="EN20" s="1">
-        <f t="shared" si="46"/>
-        <v>141.34706770745936</v>
+        <v>191.62070993110189</v>
       </c>
     </row>
     <row r="21" spans="2:144" x14ac:dyDescent="0.3">
@@ -3497,116 +3487,116 @@
         <v>77.5</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" ref="G21:P21" si="47">77.5</f>
+        <f t="shared" ref="G21:P21" si="46">77.5</f>
         <v>77.5</v>
       </c>
       <c r="H21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="K21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="M21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="N21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="O21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="P21" s="5">
+        <f t="shared" si="46"/>
+        <v>77.5</v>
+      </c>
+      <c r="Q21" s="5">
+        <f>78.4</f>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="R21" s="5">
+        <f>78.4</f>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="T21" s="5">
+        <f t="shared" ref="T21:X21" si="47">77.5</f>
+        <v>77.5</v>
+      </c>
+      <c r="U21" s="5">
         <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
-      <c r="I21" s="5">
+      <c r="V21" s="5">
         <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
-      <c r="J21" s="5">
+      <c r="W21" s="5">
         <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
-      <c r="K21" s="5">
+      <c r="X21" s="5">
         <f t="shared" si="47"/>
         <v>77.5</v>
       </c>
-      <c r="L21" s="5">
-        <f t="shared" si="47"/>
-        <v>77.5</v>
-      </c>
-      <c r="M21" s="5">
-        <f t="shared" si="47"/>
-        <v>77.5</v>
-      </c>
-      <c r="N21" s="5">
-        <f t="shared" si="47"/>
-        <v>77.5</v>
-      </c>
-      <c r="O21" s="5">
-        <f t="shared" si="47"/>
-        <v>77.5</v>
-      </c>
-      <c r="P21" s="5">
-        <f t="shared" si="47"/>
-        <v>77.5</v>
-      </c>
-      <c r="Q21" s="5">
-        <f t="shared" ref="Q21:R21" si="48">77.5</f>
-        <v>77.5</v>
-      </c>
-      <c r="R21" s="5">
+      <c r="Y21" s="5">
+        <f t="shared" ref="Y21:AI21" si="48">78.4</f>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="Z21" s="5">
         <f t="shared" si="48"/>
-        <v>77.5</v>
-      </c>
-      <c r="T21" s="5">
-        <f t="shared" ref="T21:Z21" si="49">77.5</f>
-        <v>77.5</v>
-      </c>
-      <c r="U21" s="5">
-        <f t="shared" si="49"/>
-        <v>77.5</v>
-      </c>
-      <c r="V21" s="5">
-        <f t="shared" si="49"/>
-        <v>77.5</v>
-      </c>
-      <c r="W21" s="5">
-        <f t="shared" si="49"/>
-        <v>77.5</v>
-      </c>
-      <c r="X21" s="5">
-        <f t="shared" si="49"/>
-        <v>77.5</v>
-      </c>
-      <c r="Y21" s="5">
-        <f t="shared" si="49"/>
-        <v>77.5</v>
-      </c>
-      <c r="Z21" s="5">
-        <f t="shared" si="49"/>
-        <v>77.5</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" ref="AA21:AI21" si="50">77.5</f>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" si="50"/>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" si="50"/>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" si="50"/>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="50"/>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" si="50"/>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="50"/>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="50"/>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
       <c r="AI21" s="5">
-        <f t="shared" si="50"/>
-        <v>77.5</v>
+        <f t="shared" si="48"/>
+        <v>78.400000000000006</v>
       </c>
     </row>
     <row r="22" spans="2:144" x14ac:dyDescent="0.3">
@@ -3622,116 +3612,116 @@
         <v>-0.42580645161290331</v>
       </c>
       <c r="G22" s="7">
-        <f t="shared" ref="G22:P22" si="51">G20/G21</f>
+        <f t="shared" ref="G22:P22" si="49">G20/G21</f>
         <v>-0.17935483870967744</v>
       </c>
       <c r="H22" s="7">
+        <f t="shared" si="49"/>
+        <v>-5.6774193548387135E-2</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="49"/>
+        <v>-8.5161290322580574E-2</v>
+      </c>
+      <c r="J22" s="7">
+        <f t="shared" si="49"/>
+        <v>-4.3870967741935225E-2</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="49"/>
+        <v>-0.1251612903225808</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="49"/>
+        <v>-0.14064516129032253</v>
+      </c>
+      <c r="M22" s="7">
+        <f t="shared" si="49"/>
+        <v>9.8064516129032261E-2</v>
+      </c>
+      <c r="N22" s="7">
+        <f t="shared" si="49"/>
+        <v>0.10967741935483899</v>
+      </c>
+      <c r="O22" s="7">
+        <f t="shared" si="49"/>
+        <v>5.419354838709714E-2</v>
+      </c>
+      <c r="P22" s="7">
+        <f t="shared" si="49"/>
+        <v>9.0322580645161285E-2</v>
+      </c>
+      <c r="Q22" s="7">
+        <f t="shared" ref="Q22:R22" si="50">Q20/Q21</f>
+        <v>0.12499999999999985</v>
+      </c>
+      <c r="R22" s="7">
+        <f t="shared" si="50"/>
+        <v>0.26354295918367349</v>
+      </c>
+      <c r="T22" s="7">
+        <f t="shared" ref="T22:Z22" si="51">T20/T21</f>
+        <v>-0.21032258064516121</v>
+      </c>
+      <c r="U22" s="7">
         <f t="shared" si="51"/>
-        <v>-5.6774193548387135E-2</v>
-      </c>
-      <c r="I22" s="7">
+        <v>-0.43225806451612919</v>
+      </c>
+      <c r="V22" s="7">
         <f t="shared" si="51"/>
-        <v>-8.5161290322580574E-2</v>
-      </c>
-      <c r="J22" s="7">
+        <v>-1.1819354838709675</v>
+      </c>
+      <c r="W22" s="7">
         <f t="shared" si="51"/>
-        <v>-4.3870967741935225E-2</v>
-      </c>
-      <c r="K22" s="7">
+        <v>-0.3651612903225806</v>
+      </c>
+      <c r="X22" s="7">
         <f t="shared" si="51"/>
-        <v>-0.1251612903225808</v>
-      </c>
-      <c r="L22" s="7">
+        <v>-5.8064516129031525E-2</v>
+      </c>
+      <c r="Y22" s="7">
         <f t="shared" si="51"/>
-        <v>-0.14064516129032253</v>
-      </c>
-      <c r="M22" s="7">
+        <v>0.53140010204081745</v>
+      </c>
+      <c r="Z22" s="7">
         <f t="shared" si="51"/>
-        <v>9.8064516129032261E-2</v>
-      </c>
-      <c r="N22" s="7">
-        <f t="shared" si="51"/>
-        <v>0.10967741935483899</v>
-      </c>
-      <c r="O22" s="7">
-        <f t="shared" si="51"/>
-        <v>5.419354838709714E-2</v>
-      </c>
-      <c r="P22" s="7">
-        <f t="shared" si="51"/>
-        <v>9.0322580645161285E-2</v>
-      </c>
-      <c r="Q22" s="7">
-        <f t="shared" ref="Q22:R22" si="52">Q20/Q21</f>
-        <v>0.10989116129032278</v>
-      </c>
-      <c r="R22" s="7">
+        <v>1.5581894529081626</v>
+      </c>
+      <c r="AA22" s="7">
+        <f t="shared" ref="AA22:AI22" si="52">AA20/AA21</f>
+        <v>2.769290551636352</v>
+      </c>
+      <c r="AB22" s="7">
         <f t="shared" si="52"/>
-        <v>0.21820935483870985</v>
-      </c>
-      <c r="T22" s="7">
-        <f t="shared" ref="T22:Z22" si="53">T20/T21</f>
-        <v>-0.21032258064516121</v>
-      </c>
-      <c r="U22" s="7">
-        <f t="shared" si="53"/>
-        <v>-0.43225806451612919</v>
-      </c>
-      <c r="V22" s="7">
-        <f t="shared" si="53"/>
-        <v>-1.1819354838709675</v>
-      </c>
-      <c r="W22" s="7">
-        <f t="shared" si="53"/>
-        <v>-0.3651612903225806</v>
-      </c>
-      <c r="X22" s="7">
-        <f t="shared" si="53"/>
-        <v>-5.8064516129031525E-2</v>
-      </c>
-      <c r="Y22" s="7">
-        <f t="shared" si="53"/>
-        <v>0.47261664516129054</v>
-      </c>
-      <c r="Z22" s="7">
-        <f t="shared" si="53"/>
-        <v>1.2400876045161293</v>
-      </c>
-      <c r="AA22" s="7">
-        <f t="shared" ref="AA22:AI22" si="54">AA20/AA21</f>
-        <v>2.1306601087612917</v>
-      </c>
-      <c r="AB22" s="7">
-        <f t="shared" si="54"/>
-        <v>3.059889243517163</v>
+        <v>3.8458070517470961</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" si="54"/>
-        <v>3.7861091066584733</v>
+        <f t="shared" si="52"/>
+        <v>4.6682563751137822</v>
       </c>
       <c r="AD22" s="7">
-        <f t="shared" si="54"/>
-        <v>4.2893916064974489</v>
+        <f t="shared" si="52"/>
+        <v>5.3680560705871549</v>
       </c>
       <c r="AE22" s="7">
-        <f t="shared" si="54"/>
-        <v>4.6277562524964289</v>
+        <f t="shared" si="52"/>
+        <v>5.7644213835163756</v>
       </c>
       <c r="AF22" s="7">
-        <f t="shared" si="54"/>
-        <v>4.8685426722770844</v>
+        <f t="shared" si="52"/>
+        <v>6.1144123358715596</v>
       </c>
       <c r="AG22" s="7">
-        <f t="shared" si="54"/>
-        <v>5.0560879325794774</v>
+        <f t="shared" si="52"/>
+        <v>6.485863151401694</v>
       </c>
       <c r="AH22" s="7">
-        <f t="shared" si="54"/>
-        <v>5.2510649514989378</v>
+        <f t="shared" si="52"/>
+        <v>6.8835037774735968</v>
       </c>
       <c r="AI22" s="7">
-        <f t="shared" si="54"/>
-        <v>5.454423935534555</v>
+        <f t="shared" si="52"/>
+        <v>7.3095420868482988</v>
       </c>
     </row>
     <row r="24" spans="2:144" x14ac:dyDescent="0.3">
@@ -3741,33 +3731,33 @@
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="G24" s="9">
-        <f t="shared" ref="G24:O27" si="55">G3/C3-1</f>
+        <f t="shared" ref="G24:O27" si="53">G3/C3-1</f>
         <v>0.5619335347432024</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.46388888888888902</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.1914893617021276</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.24667931688804545</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.26855123674911652</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.31605351170568574</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.32954545454545459</v>
       </c>
       <c r="P24" s="9">
@@ -3775,24 +3765,24 @@
         <v>0.34855403348554015</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:R27" si="56">Q3/M3-1</f>
-        <v>0.35000000000000009</v>
+        <f t="shared" ref="Q24:R27" si="54">Q3/M3-1</f>
+        <v>0.34122562674094703</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.32000000000000006</v>
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="9">
-        <f t="shared" ref="U24:W27" si="57">U3/T3-1</f>
+        <f t="shared" ref="U24:W27" si="55">U3/T3-1</f>
         <v>0.48034188034188019</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.77020785219399568</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.44031311154598818</v>
       </c>
       <c r="X24" s="9">
@@ -3800,47 +3790,47 @@
         <v>0.25815217391304346</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" ref="Y24:AI24" si="58">Y3/X3-1</f>
-        <v>0.33662347012239024</v>
+        <f t="shared" ref="Y24:AI24" si="56">Y3/X3-1</f>
+        <v>0.33435565154787628</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="58"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="56"/>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="58"/>
-        <v>0.25</v>
+        <f t="shared" si="56"/>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="58"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="56"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="58"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="56"/>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="58"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="56"/>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="58"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="56"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="58"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="56"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -3851,103 +3841,103 @@
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="G25" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>4.1666666666666741E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.70588235294117641</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>2.5862068965517349E-2</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>-0.24516129032258072</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.12796208530805719</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>-0.12745098039215674</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" ref="P25:P27" si="59">P4/L4-1</f>
+        <f t="shared" ref="P25:P27" si="57">P4/L4-1</f>
         <v>3.3613445378151363E-2</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="56"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="54"/>
+        <v>-3.4188034188034067E-2</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
       <c r="V25" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>46.9</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.21503131524008356</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" ref="X25:AI27" si="60">X4/W4-1</f>
+        <f t="shared" ref="X25:AI27" si="58">X4/W4-1</f>
         <v>-1.0309278350515538E-2</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="60"/>
-        <v>-5.0850694444444233E-2</v>
+        <f t="shared" si="58"/>
+        <v>-6.3888888888888773E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3958,106 +3948,106 @@
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="G26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>-0.2168674698795181</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>8.3333333333333259E-2</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.12307692307692308</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.43076923076923079</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>1.1666666666666665</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.96923076923076934</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>0.98630136986301364</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="56"/>
-        <v>0.95</v>
+        <f t="shared" si="54"/>
+        <v>0.81720430107526854</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.94999999999999973</v>
       </c>
       <c r="T26" s="9"/>
       <c r="U26" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.13063063063063063</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>7.9681274900398336E-2</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>-5.9040590405904148E-2</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.415686274509804</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="60"/>
-        <v>0.96080332409972291</v>
+        <f t="shared" si="58"/>
+        <v>0.92659279778393344</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.8</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.5</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.35000000000000009</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK26" t="s">
@@ -4074,107 +4064,107 @@
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="G27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.33725490196078445</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.45081967213114749</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.14809384164222861</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.19915254237288149</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.18066157760814261</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.32911392405063311</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>0.32311621966794402</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>0.35924617196701991</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.36978448275862097</v>
+        <f t="shared" si="54"/>
+        <v>0.34159482758620685</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.30436363636363617</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.39653035935563796</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1.0257320319432122</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.33377135348226017</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.22003284072249607</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="60"/>
-        <v>0.3372005383580079</v>
+        <f t="shared" si="58"/>
+        <v>0.33015881561238225</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="60"/>
-        <v>0.34043042051653694</v>
+        <f t="shared" si="58"/>
+        <v>0.32481760746649813</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="60"/>
-        <v>0.27857462727607785</v>
+        <f t="shared" si="58"/>
+        <v>0.25674178347876575</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="60"/>
-        <v>0.22164659843877654</v>
+        <f t="shared" si="58"/>
+        <v>0.1867845046137917</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="60"/>
-        <v>0.15515177738228059</v>
+        <f t="shared" si="58"/>
+        <v>0.12809268661998874</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="60"/>
-        <v>0.10894448572400139</v>
+        <f t="shared" si="58"/>
+        <v>9.615349372437243E-2</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="60"/>
-        <v>8.26265062949465E-2</v>
+        <f t="shared" si="58"/>
+        <v>6.9617708808366485E-2</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="60"/>
-        <v>6.9153710591197237E-2</v>
+        <f t="shared" si="58"/>
+        <v>6.3488381596383148E-2</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="60"/>
-        <v>6.2746368851451129E-2</v>
+        <f t="shared" si="58"/>
+        <v>6.4057571943471281E-2</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="60"/>
-        <v>6.3285141906275433E-2</v>
+        <f t="shared" si="58"/>
+        <v>6.4634132363049712E-2</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="60"/>
-        <v>6.383208993329692E-2</v>
+        <f t="shared" si="58"/>
+        <v>6.5217710967147902E-2</v>
       </c>
       <c r="AK27" t="s">
         <v>60</v>
@@ -4188,47 +4178,47 @@
         <v>50</v>
       </c>
       <c r="C28" s="9">
-        <f t="shared" ref="C28:D30" si="61">(C3-C7)/C3</f>
+        <f t="shared" ref="C28:D30" si="59">(C3-C7)/C3</f>
         <v>0.78549848942598188</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.78055555555555556</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" ref="G28:O30" si="62">(G3-G7)/G3</f>
+        <f t="shared" ref="G28:O30" si="60">(G3-G7)/G3</f>
         <v>0.84526112185686653</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.87855787476280833</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.85335689045936391</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.86120401337792651</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.84902597402597391</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.84170471841704719</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.85097493036211691</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.86531130876747153</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.87301587301587291</v>
       </c>
       <c r="P28" s="9">
@@ -4236,27 +4226,27 @@
         <v>0.85327313769751689</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" ref="Q28:R28" si="63">(Q3-Q7)/Q3</f>
+        <f t="shared" ref="Q28:R28" si="61">(Q3-Q7)/Q3</f>
+        <v>0.85462097611630317</v>
+      </c>
+      <c r="R28" s="9">
+        <f t="shared" si="61"/>
         <v>0.86</v>
       </c>
-      <c r="R28" s="9">
-        <f t="shared" si="63"/>
-        <v>0.86</v>
-      </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28:W30" si="64">(T3-T7)/T3</f>
+        <f t="shared" ref="T28:W30" si="62">(T3-T7)/T3</f>
         <v>0.76752136752136746</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.79445727482678985</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.79973907371167641</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.85960144927536231</v>
       </c>
       <c r="X28" s="9">
@@ -4264,47 +4254,47 @@
         <v>0.85241180705543562</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" ref="Y28:AI28" si="65">(Y3-Y7)/Y3</f>
-        <v>0.86126577505830648</v>
+        <f t="shared" ref="Y28:AI28" si="63">(Y3-Y7)/Y3</f>
+        <v>0.8598705096524264</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.87</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
+        <v>0.88</v>
+      </c>
+      <c r="AB28" s="9">
+        <f t="shared" si="63"/>
+        <v>0.88</v>
+      </c>
+      <c r="AC28" s="9">
+        <f t="shared" si="63"/>
+        <v>0.88</v>
+      </c>
+      <c r="AD28" s="9">
+        <f t="shared" si="63"/>
+        <v>0.88</v>
+      </c>
+      <c r="AE28" s="9">
+        <f t="shared" si="63"/>
         <v>0.87999999999999989</v>
       </c>
-      <c r="AB28" s="9">
-        <f t="shared" si="65"/>
+      <c r="AF28" s="9">
+        <f t="shared" si="63"/>
         <v>0.88</v>
       </c>
-      <c r="AC28" s="9">
-        <f t="shared" si="65"/>
+      <c r="AG28" s="9">
+        <f t="shared" si="63"/>
         <v>0.88</v>
       </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="65"/>
-        <v>0.88</v>
-      </c>
-      <c r="AE28" s="9">
-        <f t="shared" si="65"/>
-        <v>0.88</v>
-      </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="65"/>
-        <v>0.88</v>
-      </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="65"/>
+      <c r="AH28" s="9">
+        <f t="shared" si="63"/>
         <v>0.87999999999999989</v>
       </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="65"/>
-        <v>0.88</v>
-      </c>
       <c r="AI28" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.88</v>
       </c>
       <c r="AK28" t="s">
@@ -4312,7 +4302,7 @@
       </c>
       <c r="AL28" s="12">
         <f>NPV(AL27,Y20:EN20)</f>
-        <v>3322.3560667952738</v>
+        <v>4381.6298501998763</v>
       </c>
     </row>
     <row r="29" spans="2:144" x14ac:dyDescent="0.3">
@@ -4320,128 +4310,128 @@
         <v>51</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.1875</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>-0.58823529411764719</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>5.9999999999999963E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.25161290322580648</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.16113744075829409</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.21568627450980388</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.16806722689075629</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>4.2735042735042736E-2</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.23949579831932793</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>3.3707865168539401E-2</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29:R30" si="66">(P4-P8)/P4</f>
+        <f t="shared" ref="P29:R30" si="64">(P4-P8)/P4</f>
         <v>0.17073170731707327</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="66"/>
-        <v>0.1700000000000001</v>
+        <f t="shared" si="64"/>
+        <v>-3.539823008849545E-2</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.16999999999999996</v>
       </c>
       <c r="T29" s="9"/>
       <c r="U29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>-0.30000000000000004</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>5.2192066805845511E-2</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>0.18556701030927841</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" ref="X29:AI30" si="67">(X4-X8)/X4</f>
+        <f t="shared" ref="X29:AI30" si="65">(X4-X8)/X4</f>
         <v>0.18055555555555552</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="67"/>
-        <v>0.14797735545353116</v>
+        <f t="shared" si="65"/>
+        <v>0.10462537091988137</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" si="67"/>
-        <v>0.14999999999999997</v>
+        <f t="shared" si="65"/>
+        <v>0.15</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="67"/>
-        <v>0.14999999999999997</v>
+        <f t="shared" si="65"/>
+        <v>0.15</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AC29" s="9">
+        <f t="shared" si="65"/>
         <v>0.15000000000000005</v>
       </c>
-      <c r="AC29" s="9">
-        <f t="shared" si="67"/>
+      <c r="AD29" s="9">
+        <f t="shared" si="65"/>
+        <v>0.15000000000000005</v>
+      </c>
+      <c r="AE29" s="9">
+        <f t="shared" si="65"/>
         <v>0.15</v>
       </c>
-      <c r="AD29" s="9">
-        <f t="shared" si="67"/>
+      <c r="AF29" s="9">
+        <f t="shared" si="65"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="AG29" s="9">
+        <f t="shared" si="65"/>
+        <v>0.15</v>
+      </c>
+      <c r="AH29" s="9">
+        <f t="shared" si="65"/>
         <v>0.15000000000000005</v>
       </c>
-      <c r="AE29" s="9">
-        <f t="shared" si="67"/>
-        <v>0.15</v>
-      </c>
-      <c r="AF29" s="9">
-        <f t="shared" si="67"/>
-        <v>0.15000000000000005</v>
-      </c>
-      <c r="AG29" s="9">
-        <f t="shared" si="67"/>
-        <v>0.14999999999999997</v>
-      </c>
-      <c r="AH29" s="9">
-        <f t="shared" si="67"/>
-        <v>0.15000000000000008</v>
-      </c>
       <c r="AI29" s="9">
-        <f t="shared" si="67"/>
-        <v>0.15</v>
+        <f t="shared" si="65"/>
+        <v>0.15000000000000002</v>
       </c>
       <c r="AK29" t="s">
         <v>62</v>
       </c>
       <c r="AL29" s="12">
         <f>Main!D8</f>
-        <v>123.39999999999998</v>
+        <v>145.89999999999998</v>
       </c>
     </row>
     <row r="30" spans="2:144" x14ac:dyDescent="0.3">
@@ -4449,123 +4439,123 @@
         <v>52</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.87951807228915668</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.85</v>
       </c>
       <c r="G30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.87692307692307692</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.86153846153846148</v>
+      </c>
+      <c r="I30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.86153846153846148</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.85</v>
+      </c>
+      <c r="K30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.86153846153846148</v>
+      </c>
+      <c r="L30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.87671232876712324</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.89247311827956988</v>
+      </c>
+      <c r="N30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" si="60"/>
+        <v>0.8984375</v>
+      </c>
+      <c r="P30" s="9">
+        <f t="shared" si="64"/>
+        <v>0.8896551724137931</v>
+      </c>
+      <c r="Q30" s="9">
+        <f t="shared" si="64"/>
+        <v>0.89940828402366868</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="64"/>
+        <v>0.9</v>
+      </c>
+      <c r="T30" s="9">
         <f t="shared" si="62"/>
-        <v>0.87692307692307692</v>
-      </c>
-      <c r="H30" s="9">
+        <v>0.91891891891891886</v>
+      </c>
+      <c r="U30" s="9">
         <f t="shared" si="62"/>
-        <v>0.86153846153846148</v>
-      </c>
-      <c r="I30" s="9">
+        <v>0.85657370517928277</v>
+      </c>
+      <c r="V30" s="9">
         <f t="shared" si="62"/>
-        <v>0.86153846153846148</v>
-      </c>
-      <c r="J30" s="9">
+        <v>0.86715867158671578</v>
+      </c>
+      <c r="W30" s="9">
         <f t="shared" si="62"/>
-        <v>0.85</v>
-      </c>
-      <c r="K30" s="9">
-        <f t="shared" si="62"/>
-        <v>0.86153846153846148</v>
-      </c>
-      <c r="L30" s="9">
-        <f t="shared" si="62"/>
-        <v>0.87671232876712324</v>
-      </c>
-      <c r="M30" s="9">
-        <f t="shared" si="62"/>
-        <v>0.89247311827956988</v>
-      </c>
-      <c r="N30" s="9">
-        <f t="shared" si="62"/>
+        <v>0.86274509803921573</v>
+      </c>
+      <c r="X30" s="9">
+        <f t="shared" si="65"/>
+        <v>0.88642659279778391</v>
+      </c>
+      <c r="Y30" s="9">
+        <f t="shared" si="65"/>
+        <v>0.89741193386053197</v>
+      </c>
+      <c r="Z30" s="9">
+        <f t="shared" si="65"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="O30" s="9">
-        <f t="shared" si="62"/>
-        <v>0.8984375</v>
-      </c>
-      <c r="P30" s="9">
-        <f t="shared" si="66"/>
-        <v>0.8896551724137931</v>
-      </c>
-      <c r="Q30" s="9">
-        <f t="shared" si="66"/>
+      <c r="AA30" s="9">
+        <f t="shared" si="65"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="R30" s="9">
-        <f t="shared" si="66"/>
+      <c r="AB30" s="9">
+        <f t="shared" si="65"/>
         <v>0.9</v>
       </c>
-      <c r="T30" s="9">
-        <f t="shared" si="64"/>
-        <v>0.91891891891891886</v>
-      </c>
-      <c r="U30" s="9">
-        <f t="shared" si="64"/>
-        <v>0.85657370517928277</v>
-      </c>
-      <c r="V30" s="9">
-        <f t="shared" si="64"/>
-        <v>0.86715867158671578</v>
-      </c>
-      <c r="W30" s="9">
-        <f t="shared" si="64"/>
-        <v>0.86274509803921573</v>
-      </c>
-      <c r="X30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.88642659279778391</v>
-      </c>
-      <c r="Y30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.89759836123472492</v>
-      </c>
-      <c r="Z30" s="9">
-        <f t="shared" si="67"/>
+      <c r="AC30" s="9">
+        <f t="shared" si="65"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="AD30" s="9">
+        <f t="shared" si="65"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="AE30" s="9">
+        <f t="shared" si="65"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="AF30" s="9">
+        <f t="shared" si="65"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="AG30" s="9">
+        <f t="shared" si="65"/>
         <v>0.9</v>
       </c>
-      <c r="AA30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="AB30" s="9">
-        <f t="shared" si="67"/>
+      <c r="AH30" s="9">
+        <f t="shared" si="65"/>
         <v>0.9</v>
       </c>
-      <c r="AC30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="AD30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="AE30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="AF30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="AG30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="AH30" s="9">
-        <f t="shared" si="67"/>
-        <v>0.9</v>
-      </c>
       <c r="AI30" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>0.9</v>
       </c>
       <c r="AK30" t="s">
@@ -4573,7 +4563,7 @@
       </c>
       <c r="AL30" s="12">
         <f>AL28+AL29</f>
-        <v>3445.7560667952739</v>
+        <v>4527.5298501998759</v>
       </c>
     </row>
     <row r="31" spans="2:144" x14ac:dyDescent="0.3">
@@ -4581,47 +4571,47 @@
         <v>53</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:D31" si="68">C11/C6</f>
+        <f t="shared" ref="C31:D31" si="66">C11/C6</f>
         <v>0.68823529411764706</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>0.59836065573770492</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" ref="G31:O31" si="69">G11/G6</f>
+        <f t="shared" ref="G31:O31" si="67">G11/G6</f>
         <v>0.73313782991202348</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.77401129943502822</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.73536895674300251</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.6904487917146146</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.76756066411238821</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.75029446407538281</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.75323275862068972</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.74025974025974028</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.80405405405405406</v>
       </c>
       <c r="P31" s="9">
@@ -4629,27 +4619,27 @@
         <v>0.78509532062391685</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" ref="Q31:R31" si="70">Q11/Q6</f>
-        <v>0.8002924100821297</v>
+        <f t="shared" ref="Q31:R31" si="68">Q11/Q6</f>
+        <v>0.77991967871485934</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>0.76862638894420321</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" ref="T31:W31" si="71">T11/T6</f>
+        <f t="shared" ref="T31:W31" si="69">T11/T6</f>
         <v>0.80916976456009904</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.79858030168589167</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.6508979413053001</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>0.73103448275862071</v>
       </c>
       <c r="X31" s="9">
@@ -4657,55 +4647,55 @@
         <v>0.7515477792732167</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31:AI31" si="72">Y11/Y6</f>
-        <v>0.78794333393723448</v>
+        <f t="shared" ref="Y31:AI31" si="70">Y11/Y6</f>
+        <v>0.7827451361316512</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.81544409533877593</v>
+        <f t="shared" si="70"/>
+        <v>0.81524954422415707</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.83571942057428561</v>
+        <f t="shared" si="70"/>
+        <v>0.83479015205650808</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.84424119912130624</v>
+        <f t="shared" si="70"/>
+        <v>0.84241302064489543</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.84919803999217236</v>
+        <f t="shared" si="70"/>
+        <v>0.84684311144986135</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.85227274498324257</v>
+        <f t="shared" si="70"/>
+        <v>0.84980171640916713</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.85427162583863714</v>
+        <f t="shared" si="70"/>
+        <v>0.85163598607669366</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.855860814501744</v>
+        <f t="shared" si="70"/>
+        <v>0.85324415704828893</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.85725233989977123</v>
+        <f t="shared" si="70"/>
+        <v>0.85481543656059378</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.85861348003397231</v>
+        <f t="shared" si="70"/>
+        <v>0.85635012616812445</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="72"/>
-        <v>0.85994455023894156</v>
+        <f t="shared" si="70"/>
+        <v>0.85784852373995435</v>
       </c>
       <c r="AK31" t="s">
         <v>64</v>
       </c>
       <c r="AL31" s="13">
         <f>AL30/AI21</f>
-        <v>44.461368603809987</v>
+        <v>57.749105232141268</v>
       </c>
     </row>
     <row r="32" spans="2:144" x14ac:dyDescent="0.3">
@@ -4715,33 +4705,33 @@
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="G32" s="9">
-        <f t="shared" ref="G32:O32" si="73">G12/C12-1</f>
+        <f t="shared" ref="G32:O32" si="71">G12/C12-1</f>
         <v>5.8365758754863828E-2</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>-0.14074074074074072</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>3.6764705882352811E-3</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.1637931034482758</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.17886178861788604</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.14615384615384586</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.11355311355311337</v>
       </c>
       <c r="P32" s="9">
@@ -4749,24 +4739,24 @@
         <v>0.19629629629629619</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" ref="Q32:R32" si="74">Q12/M12-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="Q32:R32" si="72">Q12/M12-1</f>
+        <v>0.11724137931034484</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="74"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="72"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="T32" s="9"/>
       <c r="U32" s="9">
-        <f t="shared" ref="U32:W32" si="75">U12/T12-1</f>
+        <f t="shared" ref="U32:W32" si="73">U12/T12-1</f>
         <v>0.28787878787878785</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>1.0098039215686274</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>-1.4634146341463428E-2</v>
       </c>
       <c r="X32" s="9">
@@ -4774,55 +4764,55 @@
         <v>0.11980198019801969</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" ref="Y32:AI32" si="76">Y12/X12-1</f>
-        <v>0.15225464190981408</v>
+        <f t="shared" ref="Y32:AI32" si="74">Y12/X12-1</f>
+        <v>0.13595048629531403</v>
       </c>
       <c r="Z32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="74"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="74"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="74"/>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="74"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="74"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="74"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="74"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="74"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="74"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="76"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="74"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK32" t="s">
         <v>65</v>
       </c>
       <c r="AL32" s="13">
         <f>Main!D3</f>
-        <v>110.37</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="33" spans="2:38" x14ac:dyDescent="0.3">
@@ -4830,47 +4820,47 @@
         <v>55</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" ref="C33:D33" si="77">C13/C6</f>
+        <f t="shared" ref="C33:D33" si="75">C13/C6</f>
         <v>0.45490196078431372</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>0.46926229508196721</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33:O33" si="78">G13/G6</f>
+        <f t="shared" ref="G33:O33" si="76">G13/G6</f>
         <v>0.35630498533724342</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.32909604519774016</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.32697201017811706</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.29689298043728413</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.31545338441890164</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.28739693757361601</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.33081896551724138</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.29090909090909089</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.34073359073359066</v>
       </c>
       <c r="P33" s="9">
@@ -4878,27 +4868,27 @@
         <v>0.33708838821490467</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" ref="Q33:R33" si="79">Q13/Q6</f>
-        <v>0.32</v>
+        <f t="shared" ref="Q33:R33" si="77">Q13/Q6</f>
+        <v>0.31325301204819278</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="79"/>
-        <v>0.28499999999999998</v>
+        <f t="shared" si="77"/>
+        <v>0.28000000000000003</v>
       </c>
       <c r="T33" s="9">
-        <f t="shared" ref="T33:W33" si="80">T13/T6</f>
+        <f t="shared" ref="T33:W33" si="78">T13/T6</f>
         <v>0.37422552664188352</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>0.42147293700088734</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>0.40473061760841</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>0.32545155993431851</v>
       </c>
       <c r="X33" s="9">
@@ -4906,55 +4896,55 @@
         <v>0.30524899057873484</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" ref="Y33:AI33" si="81">Y13/Y6</f>
-        <v>0.31767922781166336</v>
+        <f t="shared" ref="Y33:AI33" si="79">Y13/Y6</f>
+        <v>0.31444270409629382</v>
       </c>
       <c r="Z33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.25</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.23</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.22</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.21</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.21</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.21000000000000002</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.21000000000000002</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.21000000000000002</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="81"/>
-        <v>0.3</v>
+        <f t="shared" si="79"/>
+        <v>0.21</v>
       </c>
       <c r="AK33" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AL33" s="14">
         <f>AL31/AL32-1</f>
-        <v>-0.59716074473307978</v>
+        <v>-1.9706242876569857E-2</v>
       </c>
     </row>
     <row r="34" spans="2:38" x14ac:dyDescent="0.3">
@@ -4964,33 +4954,33 @@
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="G34" s="9">
-        <f t="shared" ref="G34:O34" si="82">G14/C14-1</f>
+        <f t="shared" ref="G34:O34" si="80">G14/C14-1</f>
         <v>0</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>-2.34375E-2</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>9.090909090909105E-2</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0.16799999999999993</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>7.8014184397163122E-2</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0.2890625</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>8.3333333333333259E-2</v>
       </c>
       <c r="P34" s="9">
@@ -4998,24 +4988,24 @@
         <v>0.1917808219178081</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" ref="Q34:R34" si="83">Q14/M14-1</f>
-        <v>0.19999999999999996</v>
+        <f t="shared" ref="Q34:R34" si="81">Q14/M14-1</f>
+        <v>0.31578947368421062</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="83"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="81"/>
+        <v>0.32000000000000006</v>
       </c>
       <c r="T34" s="9"/>
       <c r="U34" s="9">
-        <f t="shared" ref="U34:W34" si="84">U14/T14-1</f>
+        <f t="shared" ref="U34:W34" si="82">U14/T14-1</f>
         <v>0.95867768595041314</v>
       </c>
       <c r="V34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>1.0295358649789033</v>
       </c>
       <c r="W34" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>9.3555093555093505E-2</v>
       </c>
       <c r="X34" s="9">
@@ -5023,47 +5013,47 @@
         <v>0.1539923954372624</v>
       </c>
       <c r="Y34" s="9">
-        <f t="shared" ref="Y34:AI34" si="85">Y14/X14-1</f>
-        <v>0.17034596375617772</v>
+        <f t="shared" ref="Y34:AI34" si="83">Y14/X14-1</f>
+        <v>0.23196046128500813</v>
       </c>
       <c r="Z34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AA34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AB34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AD34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AF34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AG34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AK34" t="s">
@@ -5078,47 +5068,47 @@
         <v>57</v>
       </c>
       <c r="C35" s="9">
-        <f t="shared" ref="C35:D35" si="86">C16/C6</f>
+        <f t="shared" ref="C35:D35" si="84">C16/C6</f>
         <v>-0.52941176470588225</v>
       </c>
       <c r="D35" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>-0.68647540983606581</v>
       </c>
       <c r="G35" s="9">
-        <f t="shared" ref="G35:O35" si="87">G16/G6</f>
+        <f t="shared" ref="G35:O35" si="85">G16/G6</f>
         <v>-0.21554252199413493</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>-5.9322033898305128E-2</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>-8.3969465648854894E-2</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>-5.2934407364786877E-2</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>-8.045977011494268E-2</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>-2.7090694935217867E-2</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>-5.387931034482759E-2</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>4.8484848484848672E-2</v>
       </c>
       <c r="O35" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>1.9305019305019579E-2</v>
       </c>
       <c r="P35" s="9">
@@ -5126,27 +5116,27 @@
         <v>1.7331022530329292E-2</v>
       </c>
       <c r="Q35" s="9">
-        <f t="shared" ref="Q35:R35" si="88">Q16/Q6</f>
-        <v>7.4442635073476329E-2</v>
+        <f t="shared" ref="Q35:R35" si="86">Q16/Q6</f>
+        <v>4.5783132530120389E-2</v>
       </c>
       <c r="R35" s="9">
-        <f t="shared" si="88"/>
-        <v>0.12472453436350851</v>
+        <f t="shared" si="86"/>
+        <v>0.12251596373146414</v>
       </c>
       <c r="T35" s="9">
-        <f t="shared" ref="T35:W35" si="89">T16/T6</f>
+        <f t="shared" ref="T35:W35" si="87">T16/T6</f>
         <v>-0.20570012391573722</v>
       </c>
       <c r="U35" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>-0.28571428571428592</v>
       </c>
       <c r="V35" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>-0.41349102058694687</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>-9.8850574712643663E-2</v>
       </c>
       <c r="X35" s="9">
@@ -5154,48 +5144,48 @@
         <v>-2.1534320323014649E-2</v>
       </c>
       <c r="Y35" s="9">
-        <f t="shared" ref="Y35:AI35" si="90">Y16/Y6</f>
-        <v>6.4925619501982848E-2</v>
+        <f t="shared" ref="Y35:AI35" si="88">Y16/Y6</f>
+        <v>5.6981264949793158E-2</v>
       </c>
       <c r="Z35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.1579052135109931</v>
+        <f t="shared" si="88"/>
+        <v>0.18409208315619402</v>
       </c>
       <c r="AA35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.21701367333768576</v>
+        <f t="shared" si="88"/>
+        <v>0.27533882092193596</v>
       </c>
       <c r="AB35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.25727087365378992</v>
+        <f t="shared" si="88"/>
+        <v>0.32883264938686241</v>
       </c>
       <c r="AC35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.27592887814262734</v>
+        <f t="shared" si="88"/>
+        <v>0.35653245666608663</v>
       </c>
       <c r="AD35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.28120770800057698</v>
+        <f t="shared" si="88"/>
+        <v>0.37604629186901634</v>
       </c>
       <c r="AE35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.27885666144675347</v>
+        <f t="shared" si="88"/>
+        <v>0.37775478816852165</v>
       </c>
       <c r="AF35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.27249981801457868</v>
+        <f t="shared" si="88"/>
+        <v>0.37757613012133123</v>
       </c>
       <c r="AG35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.2639583750634158</v>
+        <f t="shared" si="88"/>
+        <v>0.37735014454758181</v>
       </c>
       <c r="AH35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.25519217881877199</v>
+        <f t="shared" si="88"/>
+        <v>0.37707795252457132</v>
       </c>
       <c r="AI35" s="9">
-        <f t="shared" si="90"/>
-        <v>0.24620760387774684</v>
+        <f t="shared" si="88"/>
+        <v>0.37676075071323673</v>
       </c>
     </row>
     <row r="36" spans="2:38" x14ac:dyDescent="0.3">
@@ -5203,47 +5193,47 @@
         <v>28</v>
       </c>
       <c r="C36" s="9">
-        <f t="shared" ref="C36:D36" si="91">C19/C18</f>
+        <f t="shared" ref="C36:D36" si="89">C19/C18</f>
         <v>-3.9840637450199211E-3</v>
       </c>
       <c r="D36" s="9">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>3.021148036253776E-3</v>
       </c>
       <c r="G36" s="9">
-        <f t="shared" ref="G36:O36" si="92">G19/G18</f>
+        <f t="shared" ref="G36:O36" si="90">G19/G18</f>
         <v>-7.2463768115942021E-3</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-7.3170731707317013E-2</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>2.9411764705882377E-2</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-0.13333333333333422</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-0.16867469879518049</v>
       </c>
       <c r="L36" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-1.018518518518519</v>
       </c>
       <c r="M36" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-1.6206896551724137</v>
       </c>
       <c r="N36" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-0.37096774193548243</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>-4.9999999999999649E-2</v>
       </c>
       <c r="P36" s="9">
@@ -5251,27 +5241,27 @@
         <v>-6.0606060606060615E-2</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" ref="Q36:R36" si="93">Q19/Q18</f>
+        <f t="shared" ref="Q36:R36" si="91">Q19/Q18</f>
+        <v>3.9215686274509852E-2</v>
+      </c>
+      <c r="R36" s="9">
+        <f t="shared" si="91"/>
         <v>0.1</v>
       </c>
-      <c r="R36" s="9">
-        <f t="shared" si="93"/>
-        <v>0.1</v>
-      </c>
       <c r="T36" s="9">
-        <f t="shared" ref="T36:W36" si="94">T19/T18</f>
+        <f t="shared" ref="T36:W36" si="92">T19/T18</f>
         <v>0</v>
       </c>
       <c r="U36" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>2.9761904761904752E-3</v>
       </c>
       <c r="V36" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>-3.2858707557502742E-3</v>
       </c>
       <c r="W36" s="9">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>-2.1660649819494587E-2</v>
       </c>
       <c r="X36" s="9">
@@ -5279,47 +5269,47 @@
         <v>2.1739130434782879E-2</v>
       </c>
       <c r="Y36" s="9">
-        <f t="shared" ref="Y36:AI36" si="95">Y19/Y18</f>
-        <v>5.7274966476291517E-2</v>
+        <f t="shared" ref="Y36:AI36" si="93">Y19/Y18</f>
+        <v>4.789467044750241E-2</v>
       </c>
       <c r="Z36" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AA36" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AB36" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="AD36" s="9">
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
-      <c r="AD36" s="9">
-        <f t="shared" si="95"/>
+      <c r="AE36" s="9">
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
-      <c r="AE36" s="9">
-        <f t="shared" si="95"/>
+      <c r="AF36" s="9">
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
-      <c r="AF36" s="9">
-        <f t="shared" si="95"/>
+      <c r="AG36" s="9">
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
-      <c r="AG36" s="9">
-        <f t="shared" si="95"/>
+      <c r="AH36" s="9">
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
-      <c r="AH36" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
-      </c>
       <c r="AI36" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
     </row>
@@ -5328,47 +5318,47 @@
         <v>58</v>
       </c>
       <c r="C37" s="9">
-        <f t="shared" ref="C37:D37" si="96">C20/C6</f>
+        <f t="shared" ref="C37:D37" si="94">C20/C6</f>
         <v>-0.49411764705882344</v>
       </c>
       <c r="D37" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>-0.67622950819672145</v>
       </c>
       <c r="G37" s="9">
-        <f t="shared" ref="G37:O37" si="97">G20/G6</f>
+        <f t="shared" ref="G37:O37" si="95">G20/G6</f>
         <v>-0.20381231671554254</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>-6.2146892655367277E-2</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>-8.3969465648854894E-2</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>-3.9125431530494588E-2</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>-0.12388250319284817</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>-0.12838633686690218</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>8.1896551724137942E-2</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>7.3593073593073766E-2</v>
       </c>
       <c r="O37" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>4.0540540540540813E-2</v>
       </c>
       <c r="P37" s="9">
@@ -5376,27 +5366,27 @@
         <v>6.0658578856152515E-2</v>
       </c>
       <c r="Q37" s="9">
-        <f t="shared" ref="Q37:R37" si="98">Q20/Q6</f>
-        <v>6.6998371566128687E-2</v>
+        <f t="shared" ref="Q37:R37" si="96">Q20/Q6</f>
+        <v>7.8714859437750903E-2</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" si="98"/>
-        <v>0.11225208092715766</v>
+        <f t="shared" si="96"/>
+        <v>0.13714715838942212</v>
       </c>
       <c r="T37" s="9">
-        <f t="shared" ref="T37:W37" si="99">T20/T6</f>
+        <f t="shared" ref="T37:W37" si="97">T20/T6</f>
         <v>-0.2019826517967781</v>
       </c>
       <c r="U37" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>-0.29724933451641544</v>
       </c>
       <c r="V37" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>-0.40122645641699506</v>
       </c>
       <c r="W37" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>-9.2939244663382589E-2</v>
       </c>
       <c r="X37" s="9">
@@ -5404,48 +5394,48 @@
         <v>-1.2113055181695673E-2</v>
       </c>
       <c r="Y37" s="9">
-        <f t="shared" ref="Y37:AI37" si="100">Y20/Y6</f>
-        <v>7.3731887996457149E-2</v>
+        <f t="shared" ref="Y37:AI37" si="98">Y20/Y6</f>
+        <v>8.430928010296404E-2</v>
       </c>
       <c r="Z37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.1443292758747366</v>
+        <f t="shared" si="98"/>
+        <v>0.18660269701131529</v>
       </c>
       <c r="AA37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.1939501676355713</v>
+        <f t="shared" si="98"/>
+        <v>0.26388829400044861</v>
       </c>
       <c r="AB37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.22800065848769366</v>
+        <f t="shared" si="98"/>
+        <v>0.30879284279739899</v>
       </c>
       <c r="AC37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.24422182305133303</v>
+        <f t="shared" si="98"/>
+        <v>0.33226886619648899</v>
       </c>
       <c r="AD37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.24950384088546579</v>
+        <f t="shared" si="98"/>
+        <v>0.34856246773506583</v>
       </c>
       <c r="AE37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.24864135184671918</v>
+        <f t="shared" si="98"/>
+        <v>0.34993768474296949</v>
       </c>
       <c r="AF37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.24465929246655138</v>
+        <f t="shared" si="98"/>
+        <v>0.3490253462858573</v>
       </c>
       <c r="AG37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.23908246404283431</v>
+        <f t="shared" si="98"/>
+        <v>0.34794043200840979</v>
       </c>
       <c r="AH37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.23352358531027989</v>
+        <f t="shared" si="98"/>
+        <v>0.34685366419666014</v>
       </c>
       <c r="AI37" s="9">
-        <f t="shared" si="100"/>
-        <v>0.22801276591921607</v>
+        <f t="shared" si="98"/>
+        <v>0.34577096664511248</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LIF.xlsx
+++ b/Financial Analysis/LIF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E26C273-7015-4052-BDBE-3F67BC858434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0278A6-4473-4D2C-A958-72A2A9BCEC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{011E3A81-6E3D-4A18-A3DD-9F9C3A2571F0}"/>
   </bookViews>
@@ -232,7 +232,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -770,14 +770,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>58.91</v>
+        <v>47.51</v>
       </c>
       <c r="E3" s="3">
-        <v>46052</v>
+        <v>46077</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46077</v>
       </c>
       <c r="G3" s="3">
         <v>46079</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>4618.5439999999999</v>
+        <v>3724.7840000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -843,7 +843,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>4472.6440000000002</v>
+        <v>3578.884</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +860,7 @@
     <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
     <col min="37" max="37" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="17.33203125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:38" x14ac:dyDescent="0.3">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AL32" s="13">
         <f>Main!D3</f>
-        <v>58.91</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="33" spans="2:38" x14ac:dyDescent="0.3">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AL33" s="14">
         <f>AL31/AL32-1</f>
-        <v>-1.9706242876569857E-2</v>
+        <v>0.21551473862642112</v>
       </c>
     </row>
     <row r="34" spans="2:38" x14ac:dyDescent="0.3">
